--- a/metabolomics_analysis/metabolites_for_sara.xlsx
+++ b/metabolomics_analysis/metabolites_for_sara.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/laurenbell/Desktop/networks/metabolomics_analysis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{231C1C81-2093-C249-A021-A7DF1E093338}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD46A52E-F891-2844-9A11-B567D3986F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="26420" windowHeight="15780" xr2:uid="{11D052C1-3FE8-A645-8B41-A66CF54B9550}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="26420" windowHeight="15780" activeTab="1" xr2:uid="{11D052C1-3FE8-A645-8B41-A66CF54B9550}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="External IDs" sheetId="1" r:id="rId1"/>
+    <sheet name="De-Silylated Names" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$935</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'External IDs'!$A$1:$F$935</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3132" uniqueCount="1761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3267" uniqueCount="1823">
   <si>
     <t>Pyrimidine, 5-methyl-2,4-bis[(trimethylsilyl)oxy]-</t>
   </si>
@@ -5322,6 +5323,192 @@
   </si>
   <si>
     <t>HMDB0034144</t>
+  </si>
+  <si>
+    <t>De-Silyated Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3-(Nona-4,7-dienoyl)oxirane-2-carboxamide </t>
+  </si>
+  <si>
+    <t>4-1H-imidazol-2-amine</t>
+  </si>
+  <si>
+    <t>1,3-bis(ethynyl)benzene</t>
+  </si>
+  <si>
+    <t>2-Hexenoic acid</t>
+  </si>
+  <si>
+    <t>2,6-Dimethyl-N-(1,3-thiazinan-2-ylidene)aniline</t>
+  </si>
+  <si>
+    <t>1,2-Butadiene, 1,1,4-triphenyl-</t>
+  </si>
+  <si>
+    <t>3'-oxy-beta-naphthoflavone</t>
+  </si>
+  <si>
+    <t>7-amino-4-methylcoumarin</t>
+  </si>
+  <si>
+    <t>Monoacetin</t>
+  </si>
+  <si>
+    <t>Benzeneethanamine, N-[(pentafluorophenyl)methylene]-4-O</t>
+  </si>
+  <si>
+    <t>beta-d-Fructopyranose, 1-deoxy-1-(4-morpholinyl)-2,3,4,5-tetrakis-O-</t>
+  </si>
+  <si>
+    <t>beta-D-Galactofuranose, 1,2,3,5,6-pentakis-O-</t>
+  </si>
+  <si>
+    <t>Acetylene</t>
+  </si>
+  <si>
+    <t>Butanal, 2,3,4-tris(oxy)-, O-methyloxime, [R-(R*,R*)]-</t>
+  </si>
+  <si>
+    <t>Butanoic acid, 2-methyl-3-oxy-</t>
+  </si>
+  <si>
+    <t>Cetaben</t>
+  </si>
+  <si>
+    <t>cis-4-cyclohexyl-carboxylate</t>
+  </si>
+  <si>
+    <t>Morpholine, 4-(2,3,4,6-tetrakis-O-alpha-d-mannopyranosyl)-</t>
+  </si>
+  <si>
+    <t>N-hexanamide</t>
+  </si>
+  <si>
+    <t>N-isobutyl-4,5-dihydro-1H-imidazole-1-carboxamide</t>
+  </si>
+  <si>
+    <t>N,9-6-oxy-9H-purin-2-amine</t>
+  </si>
+  <si>
+    <t>Carbamate</t>
+  </si>
+  <si>
+    <t>Pentanedioic acid, 3-methyl-3-(oxy)-</t>
+  </si>
+  <si>
+    <t>Pentenoic acid, 4-(oxy)-</t>
+  </si>
+  <si>
+    <t>Tacrine</t>
+  </si>
+  <si>
+    <t>Thymine, 1,3-dimethyl-6-(oxymethyl)-</t>
+  </si>
+  <si>
+    <t>Pyrimidine, 5-methyl-2,4-bis(oxy)-</t>
+  </si>
+  <si>
+    <t>Oct-2-enoate</t>
+  </si>
+  <si>
+    <t>(5-benzyl-3,6-dioxopiperazin-2-yl)acetate</t>
+  </si>
+  <si>
+    <t>1H-Indole-2-carboxylic acid, 5-ethyl</t>
+  </si>
+  <si>
+    <t>3-(thio)propanoate</t>
+  </si>
+  <si>
+    <t>(2R)-Pyrrolidine-1,2-dicarboxylic acid, bis(tert-butyl) ester</t>
+  </si>
+  <si>
+    <t>1-(2,5-Dimethoxyphenyl)-1-(oxy)propan-2-amine</t>
+  </si>
+  <si>
+    <t>1-(tert-Butyl)-4-methyl-1H-pyrazole</t>
+  </si>
+  <si>
+    <t>1,2-Cinnolinedicarboxylic acid, 1,2,3,5,6,7,8,8a-octahydro-, diethyl ester</t>
+  </si>
+  <si>
+    <t>1-Pentene, 1,3-diphenyl-</t>
+  </si>
+  <si>
+    <t>2,3-Butanediol, monoacetate</t>
+  </si>
+  <si>
+    <t>2,5-Bis((tert-butyl)oxy)-4,4H-imidazole</t>
+  </si>
+  <si>
+    <t>2-Methylcyclohexylamine, tert.-butyl ether</t>
+  </si>
+  <si>
+    <t>2-Oxiraneethanol, 2-t-butyloxymethyl- acetate</t>
+  </si>
+  <si>
+    <t>3,3-Bis[4-(oxy)phenyl]-2-benzofuran-1(3H)-one</t>
+  </si>
+  <si>
+    <t>3,5-Dimethoxy-4-(tert.-butyl)oxybenzaldehyde</t>
+  </si>
+  <si>
+    <t>3-Hydroxymethyl-2-oxypentane</t>
+  </si>
+  <si>
+    <t>5-Ethyl-1,3-dioxane-5-methanol</t>
+  </si>
+  <si>
+    <t>5-Nonanol</t>
+  </si>
+  <si>
+    <t>6-Aminocaproic acid</t>
+  </si>
+  <si>
+    <t>9-Ethyl-9H-carbazol-3-amine</t>
+  </si>
+  <si>
+    <t>Kojic acid</t>
+  </si>
+  <si>
+    <t>L-Histidine</t>
+  </si>
+  <si>
+    <t>N-Methyl-1-(oxy)-1-[4-(oxy)phenyl]propan-2-amine</t>
+  </si>
+  <si>
+    <t>Norleucine</t>
+  </si>
+  <si>
+    <t>Oxymorphone</t>
+  </si>
+  <si>
+    <t>Propanoic acid, 3-(oxy)-2-methyl-</t>
+  </si>
+  <si>
+    <t>Propanoic acid, isopropyl ester</t>
+  </si>
+  <si>
+    <t>3-Buten-2-one, 3-hydroxy-</t>
+  </si>
+  <si>
+    <t>Butanoic acid, 2,4-o-bis(oxy)-</t>
+  </si>
+  <si>
+    <t>5-Cholesten-3beta, 7alpha-bis(oxy)-</t>
+  </si>
+  <si>
+    <t>2-Butenoic acid, 3-(oxy)</t>
+  </si>
+  <si>
+    <t>5-methyl-2,3-dihydro-1,2-oxazol-3-ol</t>
+  </si>
+  <si>
+    <t>oxohexanoic acid</t>
+  </si>
+  <si>
+    <t>Silyated ID in PubChem</t>
   </si>
 </sst>
 </file>
@@ -5409,7 +5596,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -5420,6 +5607,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5775,6 +5963,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{922CBA57-B4CC-9E42-A0F6-E5FE0A9FA5EC}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:F935"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5811,7 +6000,7 @@
         <v>793</v>
       </c>
       <c r="C2" s="1" t="b">
-        <f>ISNUMBER(SEARCH("trimethylsilyl",A2))</f>
+        <f>ISNUMBER(SEARCH("silyl",A2))</f>
         <v>1</v>
       </c>
       <c r="D2">
@@ -5821,7 +6010,7 @@
         <v>798</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>38</v>
       </c>
@@ -5829,11 +6018,11 @@
         <v>793</v>
       </c>
       <c r="C3" s="1" t="b">
-        <f t="shared" ref="C3:C66" si="0">ISNUMBER(SEARCH("trimethylsilyl",A3))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ref="C3:C66" si="0">ISNUMBER(SEARCH("silyl",A3))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>39</v>
       </c>
@@ -5845,7 +6034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>40</v>
       </c>
@@ -5857,7 +6046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>41</v>
       </c>
@@ -5869,7 +6058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>42</v>
       </c>
@@ -5881,7 +6070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>43</v>
       </c>
@@ -5893,7 +6082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>44</v>
       </c>
@@ -5914,7 +6103,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>45</v>
       </c>
@@ -5932,7 +6121,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>46</v>
       </c>
@@ -5950,7 +6139,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>47</v>
       </c>
@@ -5968,7 +6157,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>48</v>
       </c>
@@ -5989,7 +6178,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>49</v>
       </c>
@@ -6007,7 +6196,7 @@
         <v>804</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>50</v>
       </c>
@@ -6025,7 +6214,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>51</v>
       </c>
@@ -6043,7 +6232,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>52</v>
       </c>
@@ -6064,7 +6253,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>53</v>
       </c>
@@ -6085,7 +6274,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>54</v>
       </c>
@@ -6106,7 +6295,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>55</v>
       </c>
@@ -6142,7 +6331,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>56</v>
       </c>
@@ -6163,7 +6352,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>57</v>
       </c>
@@ -6184,7 +6373,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>58</v>
       </c>
@@ -6205,7 +6394,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>59</v>
       </c>
@@ -6226,7 +6415,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>60</v>
       </c>
@@ -6244,7 +6433,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>61</v>
       </c>
@@ -6265,7 +6454,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>62</v>
       </c>
@@ -6277,7 +6466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>63</v>
       </c>
@@ -6298,7 +6487,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>64</v>
       </c>
@@ -6316,7 +6505,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>65</v>
       </c>
@@ -6355,7 +6544,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>66</v>
       </c>
@@ -6391,7 +6580,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>67</v>
       </c>
@@ -6409,7 +6598,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>68</v>
       </c>
@@ -6427,7 +6616,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>69</v>
       </c>
@@ -6439,7 +6628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
         <v>70</v>
       </c>
@@ -6451,7 +6640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
         <v>71</v>
       </c>
@@ -6472,7 +6661,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
         <v>72</v>
       </c>
@@ -6493,7 +6682,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
         <v>73</v>
       </c>
@@ -6514,7 +6703,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
         <v>74</v>
       </c>
@@ -6532,7 +6721,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
         <v>75</v>
       </c>
@@ -6553,7 +6742,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
         <v>76</v>
       </c>
@@ -6571,7 +6760,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
         <v>77</v>
       </c>
@@ -6589,7 +6778,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
         <v>78</v>
       </c>
@@ -6607,7 +6796,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
         <v>79</v>
       </c>
@@ -6625,7 +6814,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
         <v>80</v>
       </c>
@@ -6643,7 +6832,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
         <v>81</v>
       </c>
@@ -6661,7 +6850,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
         <v>82</v>
       </c>
@@ -6682,7 +6871,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
         <v>83</v>
       </c>
@@ -6700,7 +6889,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
         <v>84</v>
       </c>
@@ -6721,7 +6910,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
         <v>85</v>
       </c>
@@ -6739,7 +6928,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
         <v>86</v>
       </c>
@@ -6760,7 +6949,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
         <v>87</v>
       </c>
@@ -6793,7 +6982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>88</v>
       </c>
@@ -6814,7 +7003,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>89</v>
       </c>
@@ -6832,7 +7021,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>90</v>
       </c>
@@ -6850,7 +7039,7 @@
         <v>845</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>91</v>
       </c>
@@ -6868,7 +7057,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>92</v>
       </c>
@@ -6889,7 +7078,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>93</v>
       </c>
@@ -6910,7 +7099,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>94</v>
       </c>
@@ -6931,7 +7120,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>95</v>
       </c>
@@ -6952,7 +7141,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>96</v>
       </c>
@@ -6970,7 +7159,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>97</v>
       </c>
@@ -6988,7 +7177,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>98</v>
       </c>
@@ -6996,7 +7185,7 @@
         <v>793</v>
       </c>
       <c r="C67" s="1" t="b">
-        <f t="shared" ref="C67:C130" si="1">ISNUMBER(SEARCH("trimethylsilyl",A67))</f>
+        <f t="shared" ref="C67:C130" si="1">ISNUMBER(SEARCH("silyl",A67))</f>
         <v>0</v>
       </c>
       <c r="D67">
@@ -7009,7 +7198,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>99</v>
       </c>
@@ -7027,7 +7216,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>100</v>
       </c>
@@ -7048,7 +7237,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>101</v>
       </c>
@@ -7060,7 +7249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>102</v>
       </c>
@@ -7081,7 +7270,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>103</v>
       </c>
@@ -7093,7 +7282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>104</v>
       </c>
@@ -7111,7 +7300,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>105</v>
       </c>
@@ -7132,7 +7321,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>106</v>
       </c>
@@ -7150,7 +7339,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>107</v>
       </c>
@@ -7168,7 +7357,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>108</v>
       </c>
@@ -7186,7 +7375,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
         <v>109</v>
       </c>
@@ -7204,7 +7393,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
         <v>110</v>
       </c>
@@ -7222,7 +7411,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
         <v>111</v>
       </c>
@@ -7258,7 +7447,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
         <v>112</v>
       </c>
@@ -7276,7 +7465,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
         <v>113</v>
       </c>
@@ -7294,7 +7483,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
         <v>114</v>
       </c>
@@ -7312,7 +7501,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
         <v>115</v>
       </c>
@@ -7333,7 +7522,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
         <v>116</v>
       </c>
@@ -7351,7 +7540,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
         <v>117</v>
       </c>
@@ -7390,7 +7579,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
         <v>118</v>
       </c>
@@ -7408,7 +7597,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
         <v>119</v>
       </c>
@@ -7420,7 +7609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
         <v>120</v>
       </c>
@@ -7438,7 +7627,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
         <v>121</v>
       </c>
@@ -7456,7 +7645,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
         <v>122</v>
       </c>
@@ -7477,7 +7666,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
         <v>123</v>
       </c>
@@ -7498,7 +7687,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
         <v>124</v>
       </c>
@@ -7519,7 +7708,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
         <v>125</v>
       </c>
@@ -7540,7 +7729,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
         <v>126</v>
       </c>
@@ -7561,7 +7750,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
         <v>127</v>
       </c>
@@ -7579,7 +7768,7 @@
         <v>881</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
         <v>128</v>
       </c>
@@ -7591,7 +7780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
         <v>129</v>
       </c>
@@ -7609,7 +7798,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
         <v>130</v>
       </c>
@@ -7642,7 +7831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
         <v>131</v>
       </c>
@@ -7660,7 +7849,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
         <v>132</v>
       </c>
@@ -7672,7 +7861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
         <v>133</v>
       </c>
@@ -7693,7 +7882,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
         <v>134</v>
       </c>
@@ -7711,7 +7900,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
         <v>135</v>
       </c>
@@ -7732,7 +7921,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
         <v>136</v>
       </c>
@@ -7753,7 +7942,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
         <v>137</v>
       </c>
@@ -7774,7 +7963,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
         <v>138</v>
       </c>
@@ -7795,7 +7984,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
         <v>139</v>
       </c>
@@ -7816,7 +8005,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
         <v>140</v>
       </c>
@@ -7837,7 +8026,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
         <v>141</v>
       </c>
@@ -7858,7 +8047,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
         <v>142</v>
       </c>
@@ -7879,7 +8068,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
         <v>143</v>
       </c>
@@ -7903,7 +8092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
         <v>144</v>
       </c>
@@ -7924,7 +8113,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
         <v>145</v>
       </c>
@@ -7936,7 +8125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
         <v>146</v>
       </c>
@@ -7954,7 +8143,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
         <v>147</v>
       </c>
@@ -7972,7 +8161,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
         <v>148</v>
       </c>
@@ -7993,7 +8182,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
         <v>149</v>
       </c>
@@ -8011,7 +8200,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
         <v>150</v>
       </c>
@@ -8050,7 +8239,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
         <v>151</v>
       </c>
@@ -8068,7 +8257,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
         <v>152</v>
       </c>
@@ -8080,7 +8269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
         <v>153</v>
       </c>
@@ -8098,7 +8287,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
         <v>154</v>
       </c>
@@ -8119,7 +8308,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
         <v>155</v>
       </c>
@@ -8140,7 +8329,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
         <v>156</v>
       </c>
@@ -8166,7 +8355,7 @@
         <v>793</v>
       </c>
       <c r="C131" s="1" t="b">
-        <f t="shared" ref="C131:C194" si="2">ISNUMBER(SEARCH("trimethylsilyl",A131))</f>
+        <f t="shared" ref="C131:C194" si="2">ISNUMBER(SEARCH("silyl",A131))</f>
         <v>1</v>
       </c>
     </row>
@@ -8188,7 +8377,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
         <v>157</v>
       </c>
@@ -8209,7 +8398,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
         <v>158</v>
       </c>
@@ -8227,7 +8416,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
         <v>159</v>
       </c>
@@ -8248,7 +8437,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
         <v>160</v>
       </c>
@@ -8269,7 +8458,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
         <v>161</v>
       </c>
@@ -8287,7 +8476,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
         <v>162</v>
       </c>
@@ -8299,7 +8488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
         <v>163</v>
       </c>
@@ -8320,7 +8509,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
         <v>164</v>
       </c>
@@ -8341,7 +8530,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
         <v>165</v>
       </c>
@@ -8359,7 +8548,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
         <v>166</v>
       </c>
@@ -8377,7 +8566,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
         <v>167</v>
       </c>
@@ -8398,7 +8587,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
         <v>168</v>
       </c>
@@ -8419,7 +8608,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
         <v>169</v>
       </c>
@@ -8440,7 +8629,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
         <v>170</v>
       </c>
@@ -8461,7 +8650,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
         <v>171</v>
       </c>
@@ -8482,7 +8671,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
         <v>172</v>
       </c>
@@ -8500,7 +8689,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
         <v>173</v>
       </c>
@@ -8518,7 +8707,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
         <v>174</v>
       </c>
@@ -8536,7 +8725,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
         <v>175</v>
       </c>
@@ -8554,7 +8743,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
         <v>176</v>
       </c>
@@ -8575,7 +8764,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
         <v>177</v>
       </c>
@@ -8596,7 +8785,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
         <v>178</v>
       </c>
@@ -8614,7 +8803,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
         <v>179</v>
       </c>
@@ -8635,7 +8824,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
         <v>180</v>
       </c>
@@ -8674,7 +8863,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
         <v>181</v>
       </c>
@@ -8692,7 +8881,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
         <v>182</v>
       </c>
@@ -8710,7 +8899,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
         <v>183</v>
       </c>
@@ -8728,7 +8917,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
         <v>184</v>
       </c>
@@ -8749,7 +8938,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
         <v>185</v>
       </c>
@@ -8767,7 +8956,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
         <v>186</v>
       </c>
@@ -8788,7 +8977,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
         <v>187</v>
       </c>
@@ -8833,7 +9022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
         <v>188</v>
       </c>
@@ -8854,7 +9043,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
         <v>189</v>
       </c>
@@ -8866,7 +9055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
         <v>190</v>
       </c>
@@ -8905,7 +9094,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
         <v>191</v>
       </c>
@@ -8962,7 +9151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
         <v>192</v>
       </c>
@@ -8974,7 +9163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
         <v>193</v>
       </c>
@@ -8995,7 +9184,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
         <v>194</v>
       </c>
@@ -9013,7 +9202,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
         <v>195</v>
       </c>
@@ -9043,7 +9232,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
         <v>196</v>
       </c>
@@ -9061,7 +9250,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
         <v>197</v>
       </c>
@@ -9073,7 +9262,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
         <v>198</v>
       </c>
@@ -9091,7 +9280,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
         <v>199</v>
       </c>
@@ -9112,7 +9301,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
         <v>200</v>
       </c>
@@ -9151,7 +9340,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
         <v>201</v>
       </c>
@@ -9172,7 +9361,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
         <v>202</v>
       </c>
@@ -9193,7 +9382,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
         <v>203</v>
       </c>
@@ -9205,7 +9394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
         <v>204</v>
       </c>
@@ -9223,7 +9412,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
         <v>205</v>
       </c>
@@ -9241,7 +9430,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
         <v>206</v>
       </c>
@@ -9262,7 +9451,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
         <v>207</v>
       </c>
@@ -9280,7 +9469,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
         <v>208</v>
       </c>
@@ -9298,7 +9487,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
         <v>209</v>
       </c>
@@ -9310,7 +9499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
         <v>210</v>
       </c>
@@ -9318,11 +9507,11 @@
         <v>793</v>
       </c>
       <c r="C195" s="1" t="b">
-        <f t="shared" ref="C195:C258" si="3">ISNUMBER(SEARCH("trimethylsilyl",A195))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ref="C195:C258" si="3">ISNUMBER(SEARCH("silyl",A195))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
         <v>211</v>
       </c>
@@ -9334,7 +9523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
         <v>212</v>
       </c>
@@ -9346,7 +9535,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
         <v>213</v>
       </c>
@@ -9358,7 +9547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
         <v>214</v>
       </c>
@@ -9370,7 +9559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
         <v>215</v>
       </c>
@@ -9388,7 +9577,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
         <v>216</v>
       </c>
@@ -9406,7 +9595,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
         <v>217</v>
       </c>
@@ -9424,7 +9613,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
         <v>218</v>
       </c>
@@ -9442,7 +9631,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
         <v>219</v>
       </c>
@@ -9463,7 +9652,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
         <v>220</v>
       </c>
@@ -9481,7 +9670,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
         <v>221</v>
       </c>
@@ -9502,7 +9691,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
         <v>222</v>
       </c>
@@ -9514,7 +9703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
         <v>223</v>
       </c>
@@ -9535,7 +9724,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
         <v>224</v>
       </c>
@@ -9556,7 +9745,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
         <v>225</v>
       </c>
@@ -9574,7 +9763,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
         <v>226</v>
       </c>
@@ -9595,7 +9784,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
         <v>227</v>
       </c>
@@ -9616,7 +9805,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
         <v>228</v>
       </c>
@@ -9637,7 +9826,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
         <v>229</v>
       </c>
@@ -9658,7 +9847,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
         <v>230</v>
       </c>
@@ -9670,7 +9859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
         <v>231</v>
       </c>
@@ -9691,7 +9880,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
         <v>232</v>
       </c>
@@ -9712,7 +9901,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
         <v>233</v>
       </c>
@@ -9733,7 +9922,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
         <v>234</v>
       </c>
@@ -9751,7 +9940,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="4" t="s">
         <v>235</v>
       </c>
@@ -9769,7 +9958,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
         <v>236</v>
       </c>
@@ -9787,7 +9976,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="4" t="s">
         <v>237</v>
       </c>
@@ -9808,7 +9997,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
         <v>238</v>
       </c>
@@ -9829,7 +10018,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="4" t="s">
         <v>239</v>
       </c>
@@ -9850,7 +10039,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
         <v>240</v>
       </c>
@@ -9871,7 +10060,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="4" t="s">
         <v>241</v>
       </c>
@@ -9889,7 +10078,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
         <v>242</v>
       </c>
@@ -9907,7 +10096,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="4" t="s">
         <v>243</v>
       </c>
@@ -9928,7 +10117,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
         <v>244</v>
       </c>
@@ -9940,7 +10129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="4" t="s">
         <v>245</v>
       </c>
@@ -9958,7 +10147,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
         <v>246</v>
       </c>
@@ -9979,7 +10168,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="4" t="s">
         <v>247</v>
       </c>
@@ -9997,7 +10186,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
         <v>248</v>
       </c>
@@ -10015,7 +10204,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="4" t="s">
         <v>249</v>
       </c>
@@ -10036,7 +10225,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
         <v>250</v>
       </c>
@@ -10057,7 +10246,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="4" t="s">
         <v>251</v>
       </c>
@@ -10078,7 +10267,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
         <v>252</v>
       </c>
@@ -10099,7 +10288,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="4" t="s">
         <v>253</v>
       </c>
@@ -10120,7 +10309,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
         <v>254</v>
       </c>
@@ -10138,7 +10327,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="4" t="s">
         <v>255</v>
       </c>
@@ -10159,7 +10348,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
         <v>256</v>
       </c>
@@ -10180,7 +10369,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="4" t="s">
         <v>257</v>
       </c>
@@ -10210,7 +10399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="4" t="s">
         <v>258</v>
       </c>
@@ -10231,7 +10420,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
         <v>259</v>
       </c>
@@ -10249,7 +10438,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="4" t="s">
         <v>260</v>
       </c>
@@ -10270,7 +10459,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
         <v>261</v>
       </c>
@@ -10291,7 +10480,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="4" t="s">
         <v>262</v>
       </c>
@@ -10312,7 +10501,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
         <v>263</v>
       </c>
@@ -10333,7 +10522,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="4" t="s">
         <v>264</v>
       </c>
@@ -10354,7 +10543,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
         <v>265</v>
       </c>
@@ -10375,7 +10564,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" s="4" t="s">
         <v>266</v>
       </c>
@@ -10393,7 +10582,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
         <v>267</v>
       </c>
@@ -10414,7 +10603,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" s="4" t="s">
         <v>268</v>
       </c>
@@ -10435,7 +10624,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
         <v>269</v>
       </c>
@@ -10453,7 +10642,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" s="4" t="s">
         <v>270</v>
       </c>
@@ -10474,7 +10663,7 @@
         <v>1009</v>
       </c>
     </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
         <v>271</v>
       </c>
@@ -10486,7 +10675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" s="4" t="s">
         <v>272</v>
       </c>
@@ -10507,7 +10696,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
         <v>273</v>
       </c>
@@ -10515,7 +10704,7 @@
         <v>793</v>
       </c>
       <c r="C259" s="1" t="b">
-        <f t="shared" ref="C259:C322" si="4">ISNUMBER(SEARCH("trimethylsilyl",A259))</f>
+        <f t="shared" ref="C259:C322" si="4">ISNUMBER(SEARCH("silyl",A259))</f>
         <v>0</v>
       </c>
       <c r="D259">
@@ -10528,7 +10717,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" s="4" t="s">
         <v>274</v>
       </c>
@@ -10549,7 +10738,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
         <v>275</v>
       </c>
@@ -10570,7 +10759,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" s="4" t="s">
         <v>276</v>
       </c>
@@ -10591,7 +10780,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
         <v>277</v>
       </c>
@@ -10612,7 +10801,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" s="4" t="s">
         <v>278</v>
       </c>
@@ -10633,7 +10822,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
         <v>279</v>
       </c>
@@ -10654,7 +10843,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" s="4" t="s">
         <v>280</v>
       </c>
@@ -10675,7 +10864,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
         <v>281</v>
       </c>
@@ -10696,7 +10885,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" s="4" t="s">
         <v>282</v>
       </c>
@@ -10717,7 +10906,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
         <v>283</v>
       </c>
@@ -10729,7 +10918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" s="4" t="s">
         <v>284</v>
       </c>
@@ -10750,7 +10939,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
         <v>285</v>
       </c>
@@ -10771,7 +10960,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" s="4" t="s">
         <v>286</v>
       </c>
@@ -10792,7 +10981,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
         <v>287</v>
       </c>
@@ -10810,7 +10999,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" s="4" t="s">
         <v>288</v>
       </c>
@@ -10831,7 +11020,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
         <v>289</v>
       </c>
@@ -10849,7 +11038,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" s="4" t="s">
         <v>290</v>
       </c>
@@ -10870,7 +11059,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
         <v>291</v>
       </c>
@@ -10882,7 +11071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" s="4" t="s">
         <v>292</v>
       </c>
@@ -10900,7 +11089,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
         <v>293</v>
       </c>
@@ -10918,7 +11107,7 @@
         <v>1028</v>
       </c>
     </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" s="4" t="s">
         <v>294</v>
       </c>
@@ -10939,7 +11128,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
         <v>295</v>
       </c>
@@ -10957,7 +11146,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" s="4" t="s">
         <v>296</v>
       </c>
@@ -10978,7 +11167,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
         <v>297</v>
       </c>
@@ -10996,7 +11185,7 @@
         <v>1032</v>
       </c>
     </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" s="4" t="s">
         <v>298</v>
       </c>
@@ -11008,7 +11197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
         <v>299</v>
       </c>
@@ -11029,7 +11218,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" s="4" t="s">
         <v>300</v>
       </c>
@@ -11047,7 +11236,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
         <v>301</v>
       </c>
@@ -11065,7 +11254,7 @@
         <v>1035</v>
       </c>
     </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" s="4" t="s">
         <v>302</v>
       </c>
@@ -11083,7 +11272,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
         <v>303</v>
       </c>
@@ -11113,7 +11302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
         <v>304</v>
       </c>
@@ -11152,7 +11341,7 @@
         <v>1039</v>
       </c>
     </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
         <v>305</v>
       </c>
@@ -11191,7 +11380,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
         <v>306</v>
       </c>
@@ -11212,7 +11401,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" s="4" t="s">
         <v>307</v>
       </c>
@@ -11233,7 +11422,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" s="4" t="s">
         <v>308</v>
       </c>
@@ -11251,7 +11440,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" s="4" t="s">
         <v>309</v>
       </c>
@@ -11272,7 +11461,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" s="4" t="s">
         <v>310</v>
       </c>
@@ -11311,7 +11500,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
         <v>311</v>
       </c>
@@ -11332,7 +11521,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" s="4" t="s">
         <v>312</v>
       </c>
@@ -11368,7 +11557,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" s="4" t="s">
         <v>313</v>
       </c>
@@ -11386,7 +11575,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" s="4" t="s">
         <v>314</v>
       </c>
@@ -11407,7 +11596,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" s="4" t="s">
         <v>315</v>
       </c>
@@ -11428,7 +11617,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" s="4" t="s">
         <v>316</v>
       </c>
@@ -11449,7 +11638,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" s="4" t="s">
         <v>317</v>
       </c>
@@ -11470,7 +11659,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" s="4" t="s">
         <v>318</v>
       </c>
@@ -11488,7 +11677,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" s="4" t="s">
         <v>319</v>
       </c>
@@ -11509,7 +11698,7 @@
         <v>1057</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" s="4" t="s">
         <v>320</v>
       </c>
@@ -11530,7 +11719,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" s="4" t="s">
         <v>321</v>
       </c>
@@ -11548,7 +11737,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" s="4" t="s">
         <v>322</v>
       </c>
@@ -11566,7 +11755,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" s="4" t="s">
         <v>323</v>
       </c>
@@ -11584,7 +11773,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" s="4" t="s">
         <v>324</v>
       </c>
@@ -11605,7 +11794,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" s="4" t="s">
         <v>325</v>
       </c>
@@ -11626,7 +11815,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" s="4" t="s">
         <v>326</v>
       </c>
@@ -11644,7 +11833,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" s="4" t="s">
         <v>327</v>
       </c>
@@ -11665,7 +11854,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" s="4" t="s">
         <v>328</v>
       </c>
@@ -11686,7 +11875,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320" s="4" t="s">
         <v>329</v>
       </c>
@@ -11704,7 +11893,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321" s="4" t="s">
         <v>330</v>
       </c>
@@ -11725,7 +11914,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="322" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322" s="4" t="s">
         <v>331</v>
       </c>
@@ -11746,7 +11935,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="323" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323" s="4" t="s">
         <v>332</v>
       </c>
@@ -11754,7 +11943,7 @@
         <v>793</v>
       </c>
       <c r="C323" s="1" t="b">
-        <f t="shared" ref="C323:C386" si="5">ISNUMBER(SEARCH("trimethylsilyl",A323))</f>
+        <f t="shared" ref="C323:C386" si="5">ISNUMBER(SEARCH("silyl",A323))</f>
         <v>0</v>
       </c>
       <c r="D323">
@@ -11803,7 +11992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327" s="4" t="s">
         <v>333</v>
       </c>
@@ -11824,7 +12013,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="328" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328" s="4" t="s">
         <v>334</v>
       </c>
@@ -11842,7 +12031,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="329" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329" s="4" t="s">
         <v>335</v>
       </c>
@@ -11863,7 +12052,7 @@
         <v>1073</v>
       </c>
     </row>
-    <row r="330" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330" s="4" t="s">
         <v>336</v>
       </c>
@@ -11884,7 +12073,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="331" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331" s="4" t="s">
         <v>337</v>
       </c>
@@ -11902,7 +12091,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="332" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332" s="4" t="s">
         <v>338</v>
       </c>
@@ -11923,7 +12112,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="333" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333" s="4" t="s">
         <v>339</v>
       </c>
@@ -11944,7 +12133,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="334" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334" s="4" t="s">
         <v>340</v>
       </c>
@@ -11965,7 +12154,7 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="335" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335" s="4" t="s">
         <v>341</v>
       </c>
@@ -11983,7 +12172,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="336" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336" s="4" t="s">
         <v>342</v>
       </c>
@@ -12004,7 +12193,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="337" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" s="4" t="s">
         <v>343</v>
       </c>
@@ -12025,7 +12214,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="338" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" s="4" t="s">
         <v>344</v>
       </c>
@@ -12037,7 +12226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339" s="4" t="s">
         <v>345</v>
       </c>
@@ -12049,7 +12238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340" s="4" t="s">
         <v>346</v>
       </c>
@@ -12070,7 +12259,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="341" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" s="4" t="s">
         <v>347</v>
       </c>
@@ -12088,7 +12277,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="342" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342" s="4" t="s">
         <v>348</v>
       </c>
@@ -12109,7 +12298,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="343" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343" s="4" t="s">
         <v>349</v>
       </c>
@@ -12139,7 +12328,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="345" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" s="4" t="s">
         <v>350</v>
       </c>
@@ -12160,7 +12349,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="346" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346" s="4" t="s">
         <v>351</v>
       </c>
@@ -12178,7 +12367,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="347" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" s="4" t="s">
         <v>352</v>
       </c>
@@ -12199,7 +12388,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="348" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348" s="4" t="s">
         <v>353</v>
       </c>
@@ -12211,7 +12400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349" s="4" t="s">
         <v>354</v>
       </c>
@@ -12232,7 +12421,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="350" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350" s="4" t="s">
         <v>355</v>
       </c>
@@ -12250,7 +12439,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="351" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351" s="4" t="s">
         <v>356</v>
       </c>
@@ -12268,7 +12457,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="352" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352" s="4" t="s">
         <v>357</v>
       </c>
@@ -12286,7 +12475,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="353" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353" s="4" t="s">
         <v>358</v>
       </c>
@@ -12307,7 +12496,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="354" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354" s="4" t="s">
         <v>359</v>
       </c>
@@ -12319,7 +12508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" s="4" t="s">
         <v>360</v>
       </c>
@@ -12340,7 +12529,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="356" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" s="4" t="s">
         <v>361</v>
       </c>
@@ -12373,7 +12562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="358" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" s="4" t="s">
         <v>362</v>
       </c>
@@ -12385,7 +12574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359" s="4" t="s">
         <v>363</v>
       </c>
@@ -12406,7 +12595,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="360" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360" s="4" t="s">
         <v>364</v>
       </c>
@@ -12424,7 +12613,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="361" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361" s="4" t="s">
         <v>365</v>
       </c>
@@ -12460,7 +12649,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="363" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" s="4" t="s">
         <v>366</v>
       </c>
@@ -12481,7 +12670,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="364" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364" s="4" t="s">
         <v>367</v>
       </c>
@@ -12556,7 +12745,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="368" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" s="4" t="s">
         <v>368</v>
       </c>
@@ -12574,7 +12763,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="369" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369" s="4" t="s">
         <v>369</v>
       </c>
@@ -12595,7 +12784,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="370" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370" s="4" t="s">
         <v>370</v>
       </c>
@@ -12616,7 +12805,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="371" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" s="4" t="s">
         <v>371</v>
       </c>
@@ -12637,7 +12826,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="372" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" s="4" t="s">
         <v>372</v>
       </c>
@@ -12655,7 +12844,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="373" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373" s="4" t="s">
         <v>373</v>
       </c>
@@ -12673,7 +12862,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="374" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374" s="4" t="s">
         <v>374</v>
       </c>
@@ -12694,7 +12883,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="375" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375" s="5" t="s">
         <v>375</v>
       </c>
@@ -12715,7 +12904,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="376" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376" s="6" t="s">
         <v>376</v>
       </c>
@@ -12736,7 +12925,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="377" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377" s="6" t="s">
         <v>377</v>
       </c>
@@ -12748,7 +12937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="378" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378" s="6" t="s">
         <v>378</v>
       </c>
@@ -12760,7 +12949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="379" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" s="6" t="s">
         <v>379</v>
       </c>
@@ -12778,7 +12967,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="380" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380" s="6" t="s">
         <v>380</v>
       </c>
@@ -12799,7 +12988,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="381" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381" s="6" t="s">
         <v>381</v>
       </c>
@@ -12811,7 +13000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382" s="6" t="s">
         <v>382</v>
       </c>
@@ -12823,7 +13012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="383" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383" s="6" t="s">
         <v>265</v>
       </c>
@@ -12844,7 +13033,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="384" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384" s="6" t="s">
         <v>336</v>
       </c>
@@ -12865,7 +13054,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="385" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385" s="6" t="s">
         <v>383</v>
       </c>
@@ -12886,7 +13075,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="386" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" s="6" t="s">
         <v>384</v>
       </c>
@@ -12907,7 +13096,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="387" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387" s="6" t="s">
         <v>385</v>
       </c>
@@ -12915,11 +13104,11 @@
         <v>794</v>
       </c>
       <c r="C387" s="1" t="b">
-        <f t="shared" ref="C387:C450" si="6">ISNUMBER(SEARCH("trimethylsilyl",A387))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="388" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ref="C387:C450" si="6">ISNUMBER(SEARCH("silyl",A387))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388" s="6" t="s">
         <v>386</v>
       </c>
@@ -12937,7 +13126,7 @@
         <v>1117</v>
       </c>
     </row>
-    <row r="389" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389" s="6" t="s">
         <v>387</v>
       </c>
@@ -12958,7 +13147,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="390" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" s="6" t="s">
         <v>388</v>
       </c>
@@ -12979,7 +13168,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="391" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391" s="6" t="s">
         <v>389</v>
       </c>
@@ -13000,7 +13189,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="392" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" s="6" t="s">
         <v>390</v>
       </c>
@@ -13018,7 +13207,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="393" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393" s="6" t="s">
         <v>285</v>
       </c>
@@ -13039,7 +13228,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="394" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394" s="6" t="s">
         <v>391</v>
       </c>
@@ -13057,7 +13246,7 @@
         <v>1122</v>
       </c>
     </row>
-    <row r="395" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395" s="6" t="s">
         <v>392</v>
       </c>
@@ -13078,7 +13267,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="396" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" s="6" t="s">
         <v>393</v>
       </c>
@@ -13099,7 +13288,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="397" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397" s="6" t="s">
         <v>394</v>
       </c>
@@ -13120,7 +13309,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="398" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398" s="6" t="s">
         <v>395</v>
       </c>
@@ -13141,7 +13330,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="399" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399" s="6" t="s">
         <v>396</v>
       </c>
@@ -13153,7 +13342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="400" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400" s="6" t="s">
         <v>397</v>
       </c>
@@ -13171,7 +13360,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="401" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401" s="6" t="s">
         <v>398</v>
       </c>
@@ -13192,7 +13381,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="402" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402" s="6" t="s">
         <v>399</v>
       </c>
@@ -13213,7 +13402,7 @@
         <v>1128</v>
       </c>
     </row>
-    <row r="403" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403" s="6" t="s">
         <v>400</v>
       </c>
@@ -13231,7 +13420,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="404" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404" s="6" t="s">
         <v>401</v>
       </c>
@@ -13252,7 +13441,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="405" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405" s="6" t="s">
         <v>280</v>
       </c>
@@ -13273,7 +13462,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="406" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406" s="6" t="s">
         <v>360</v>
       </c>
@@ -13294,7 +13483,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="407" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407" s="6" t="s">
         <v>402</v>
       </c>
@@ -13315,7 +13504,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="408" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408" s="6" t="s">
         <v>136</v>
       </c>
@@ -13336,7 +13525,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="409" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409" s="6" t="s">
         <v>403</v>
       </c>
@@ -13354,7 +13543,7 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="410" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410" s="6" t="s">
         <v>404</v>
       </c>
@@ -13375,7 +13564,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="411" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411" s="6" t="s">
         <v>405</v>
       </c>
@@ -13396,7 +13585,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="412" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412" s="6" t="s">
         <v>406</v>
       </c>
@@ -13417,7 +13606,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="413" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413" s="6" t="s">
         <v>407</v>
       </c>
@@ -13435,7 +13624,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="414" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414" s="6" t="s">
         <v>275</v>
       </c>
@@ -13456,7 +13645,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="415" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415" s="6" t="s">
         <v>408</v>
       </c>
@@ -13477,7 +13666,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="416" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416" s="6" t="s">
         <v>58</v>
       </c>
@@ -13498,7 +13687,7 @@
         <v>814</v>
       </c>
     </row>
-    <row r="417" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417" s="6" t="s">
         <v>409</v>
       </c>
@@ -13510,7 +13699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="418" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418" s="6" t="s">
         <v>350</v>
       </c>
@@ -13531,7 +13720,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="419" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419" s="6" t="s">
         <v>355</v>
       </c>
@@ -13549,7 +13738,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="420" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420" s="6" t="s">
         <v>410</v>
       </c>
@@ -13567,7 +13756,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="421" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421" s="6" t="s">
         <v>411</v>
       </c>
@@ -13579,7 +13768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="422" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422" s="6" t="s">
         <v>138</v>
       </c>
@@ -13600,7 +13789,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="423" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423" s="6" t="s">
         <v>342</v>
       </c>
@@ -13621,7 +13810,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="424" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424" s="6" t="s">
         <v>412</v>
       </c>
@@ -13642,7 +13831,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="425" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425" s="6" t="s">
         <v>413</v>
       </c>
@@ -13663,7 +13852,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="426" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426" s="6" t="s">
         <v>414</v>
       </c>
@@ -13675,7 +13864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427" s="6" t="s">
         <v>415</v>
       </c>
@@ -13687,7 +13876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428" s="6" t="s">
         <v>286</v>
       </c>
@@ -13708,7 +13897,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="429" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429" s="6" t="s">
         <v>416</v>
       </c>
@@ -13720,7 +13909,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="430" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430" s="6" t="s">
         <v>417</v>
       </c>
@@ -13741,7 +13930,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="431" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431" s="6" t="s">
         <v>418</v>
       </c>
@@ -13759,7 +13948,7 @@
         <v>1142</v>
       </c>
     </row>
-    <row r="432" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432" s="6" t="s">
         <v>419</v>
       </c>
@@ -13780,7 +13969,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="433" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433" s="6" t="s">
         <v>420</v>
       </c>
@@ -13792,7 +13981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="434" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434" s="6" t="s">
         <v>421</v>
       </c>
@@ -13810,7 +13999,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="435" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435" s="6" t="s">
         <v>422</v>
       </c>
@@ -13822,7 +14011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="436" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436" s="6" t="s">
         <v>423</v>
       </c>
@@ -13840,7 +14029,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="437" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437" s="6" t="s">
         <v>424</v>
       </c>
@@ -13861,7 +14050,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="438" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438" s="6" t="s">
         <v>425</v>
       </c>
@@ -13882,7 +14071,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="439" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439" s="6" t="s">
         <v>426</v>
       </c>
@@ -13900,7 +14089,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="440" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440" s="6" t="s">
         <v>98</v>
       </c>
@@ -13921,7 +14110,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="441" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441" s="6" t="s">
         <v>427</v>
       </c>
@@ -13933,7 +14122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="442" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442" s="6" t="s">
         <v>428</v>
       </c>
@@ -13954,7 +14143,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="443" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443" s="6" t="s">
         <v>63</v>
       </c>
@@ -13975,7 +14164,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="444" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444" s="6" t="s">
         <v>88</v>
       </c>
@@ -13996,7 +14185,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="445" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445" s="6" t="s">
         <v>429</v>
       </c>
@@ -14008,7 +14197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446" s="6" t="s">
         <v>430</v>
       </c>
@@ -14029,7 +14218,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="447" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447" s="6" t="s">
         <v>431</v>
       </c>
@@ -14050,7 +14239,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="448" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448" s="6" t="s">
         <v>432</v>
       </c>
@@ -14071,7 +14260,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="449" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449" s="6" t="s">
         <v>235</v>
       </c>
@@ -14089,7 +14278,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="450" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450" s="6" t="s">
         <v>102</v>
       </c>
@@ -14110,7 +14299,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="451" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451" s="6" t="s">
         <v>433</v>
       </c>
@@ -14118,11 +14307,11 @@
         <v>794</v>
       </c>
       <c r="C451" s="1" t="b">
-        <f t="shared" ref="C451:C514" si="7">ISNUMBER(SEARCH("trimethylsilyl",A451))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="452" spans="1:6" x14ac:dyDescent="0.25">
+        <f t="shared" ref="C451:C514" si="7">ISNUMBER(SEARCH("silyl",A451))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452" s="6" t="s">
         <v>434</v>
       </c>
@@ -14134,7 +14323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453" s="6" t="s">
         <v>435</v>
       </c>
@@ -14152,7 +14341,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="454" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454" s="6" t="s">
         <v>436</v>
       </c>
@@ -14173,7 +14362,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="455" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455" s="6" t="s">
         <v>437</v>
       </c>
@@ -14185,7 +14374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456" s="6" t="s">
         <v>438</v>
       </c>
@@ -14203,7 +14392,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="457" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457" s="6" t="s">
         <v>320</v>
       </c>
@@ -14224,7 +14413,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="458" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458" s="6" t="s">
         <v>439</v>
       </c>
@@ -14242,7 +14431,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="459" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459" s="6" t="s">
         <v>112</v>
       </c>
@@ -14260,7 +14449,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="460" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460" s="6" t="s">
         <v>440</v>
       </c>
@@ -14281,7 +14470,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="461" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461" s="6" t="s">
         <v>441</v>
       </c>
@@ -14299,7 +14488,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="462" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462" s="6" t="s">
         <v>343</v>
       </c>
@@ -14320,7 +14509,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="463" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463" s="6" t="s">
         <v>442</v>
       </c>
@@ -14332,7 +14521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="464" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464" s="6" t="s">
         <v>443</v>
       </c>
@@ -14353,7 +14542,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="465" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465" s="6" t="s">
         <v>83</v>
       </c>
@@ -14371,7 +14560,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="466" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466" s="6" t="s">
         <v>444</v>
       </c>
@@ -14389,7 +14578,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="467" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467" s="6" t="s">
         <v>445</v>
       </c>
@@ -14401,7 +14590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="468" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468" s="6" t="s">
         <v>446</v>
       </c>
@@ -14422,7 +14611,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="469" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469" s="6" t="s">
         <v>447</v>
       </c>
@@ -14440,7 +14629,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="470" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470" s="6" t="s">
         <v>448</v>
       </c>
@@ -14461,7 +14650,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="471" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471" s="6" t="s">
         <v>449</v>
       </c>
@@ -14482,7 +14671,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="472" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472" s="6" t="s">
         <v>450</v>
       </c>
@@ -14503,7 +14692,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="473" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473" s="6" t="s">
         <v>451</v>
       </c>
@@ -14542,7 +14731,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="475" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475" s="6" t="s">
         <v>452</v>
       </c>
@@ -14560,7 +14749,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="476" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476" s="6" t="s">
         <v>282</v>
       </c>
@@ -14581,7 +14770,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="477" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477" s="6" t="s">
         <v>453</v>
       </c>
@@ -14602,7 +14791,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="478" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478" s="6" t="s">
         <v>454</v>
       </c>
@@ -14623,7 +14812,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="479" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479" s="6" t="s">
         <v>455</v>
       </c>
@@ -14641,7 +14830,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="480" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480" s="6" t="s">
         <v>456</v>
       </c>
@@ -14659,7 +14848,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="481" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481" s="6" t="s">
         <v>457</v>
       </c>
@@ -14677,7 +14866,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="482" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482" s="6" t="s">
         <v>458</v>
       </c>
@@ -14698,7 +14887,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="483" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483" s="6" t="s">
         <v>371</v>
       </c>
@@ -14719,7 +14908,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="484" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484" s="6" t="s">
         <v>459</v>
       </c>
@@ -14737,7 +14926,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="485" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485" s="6" t="s">
         <v>460</v>
       </c>
@@ -14758,7 +14947,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="486" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486" s="6" t="s">
         <v>461</v>
       </c>
@@ -14782,7 +14971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="488" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488" s="6" t="s">
         <v>462</v>
       </c>
@@ -14803,7 +14992,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="489" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489" s="6" t="s">
         <v>463</v>
       </c>
@@ -14821,7 +15010,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="490" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490" s="6" t="s">
         <v>464</v>
       </c>
@@ -14839,7 +15028,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="491" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491" s="6" t="s">
         <v>267</v>
       </c>
@@ -14860,7 +15049,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="492" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492" s="6" t="s">
         <v>373</v>
       </c>
@@ -14878,7 +15067,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="493" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493" s="6" t="s">
         <v>465</v>
       </c>
@@ -14899,7 +15088,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="494" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494" s="6" t="s">
         <v>466</v>
       </c>
@@ -14911,7 +15100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="495" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495" s="6" t="s">
         <v>316</v>
       </c>
@@ -14932,7 +15121,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="496" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496" s="6" t="s">
         <v>467</v>
       </c>
@@ -14950,7 +15139,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="497" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497" s="6" t="s">
         <v>468</v>
       </c>
@@ -14962,7 +15151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="498" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498" s="6" t="s">
         <v>469</v>
       </c>
@@ -14983,7 +15172,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="499" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499" s="6" t="s">
         <v>470</v>
       </c>
@@ -15004,7 +15193,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="500" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500" s="6" t="s">
         <v>471</v>
       </c>
@@ -15025,7 +15214,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="501" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501" s="6" t="s">
         <v>472</v>
       </c>
@@ -15037,7 +15226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502" s="6" t="s">
         <v>473</v>
       </c>
@@ -15055,7 +15244,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="503" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503" s="6" t="s">
         <v>474</v>
       </c>
@@ -15067,7 +15256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="504" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504" s="6" t="s">
         <v>475</v>
       </c>
@@ -15085,7 +15274,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="505" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505" s="6" t="s">
         <v>476</v>
       </c>
@@ -15097,7 +15286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506" s="6" t="s">
         <v>477</v>
       </c>
@@ -15115,7 +15304,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="507" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507" s="6" t="s">
         <v>478</v>
       </c>
@@ -15136,7 +15325,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="508" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508" s="6" t="s">
         <v>479</v>
       </c>
@@ -15157,7 +15346,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="509" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509" s="6" t="s">
         <v>480</v>
       </c>
@@ -15178,7 +15367,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="510" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510" s="6" t="s">
         <v>228</v>
       </c>
@@ -15199,7 +15388,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="511" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511" s="6" t="s">
         <v>481</v>
       </c>
@@ -15211,7 +15400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512" s="6" t="s">
         <v>223</v>
       </c>
@@ -15232,7 +15421,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="513" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513" s="6" t="s">
         <v>482</v>
       </c>
@@ -15253,7 +15442,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="514" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514" s="6" t="s">
         <v>220</v>
       </c>
@@ -15271,7 +15460,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="515" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515" s="6" t="s">
         <v>483</v>
       </c>
@@ -15279,7 +15468,7 @@
         <v>794</v>
       </c>
       <c r="C515" s="1" t="b">
-        <f t="shared" ref="C515:C578" si="8">ISNUMBER(SEARCH("trimethylsilyl",A515))</f>
+        <f t="shared" ref="C515:C578" si="8">ISNUMBER(SEARCH("silyl",A515))</f>
         <v>0</v>
       </c>
       <c r="D515">
@@ -15289,7 +15478,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="516" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516" s="6" t="s">
         <v>484</v>
       </c>
@@ -15310,7 +15499,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="517" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517" s="6" t="s">
         <v>305</v>
       </c>
@@ -15331,7 +15520,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="518" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518" s="6" t="s">
         <v>485</v>
       </c>
@@ -15352,7 +15541,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="519" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519" s="6" t="s">
         <v>486</v>
       </c>
@@ -15373,7 +15562,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="520" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520" s="6" t="s">
         <v>277</v>
       </c>
@@ -15394,7 +15583,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="521" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521" s="6" t="s">
         <v>487</v>
       </c>
@@ -15415,7 +15604,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="522" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522" s="6" t="s">
         <v>488</v>
       </c>
@@ -15433,7 +15622,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="523" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523" s="6" t="s">
         <v>489</v>
       </c>
@@ -15454,7 +15643,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="524" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524" s="6" t="s">
         <v>490</v>
       </c>
@@ -15475,7 +15664,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="525" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525" s="6" t="s">
         <v>201</v>
       </c>
@@ -15496,7 +15685,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="526" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526" s="6" t="s">
         <v>491</v>
       </c>
@@ -15517,7 +15706,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="527" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527" s="6" t="s">
         <v>154</v>
       </c>
@@ -15538,7 +15727,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="528" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528" s="6" t="s">
         <v>163</v>
       </c>
@@ -15559,7 +15748,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="529" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529" s="6" t="s">
         <v>226</v>
       </c>
@@ -15580,7 +15769,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="530" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530" s="6" t="s">
         <v>215</v>
       </c>
@@ -15598,7 +15787,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="531" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531" s="6" t="s">
         <v>254</v>
       </c>
@@ -15616,7 +15805,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="532" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532" s="6" t="s">
         <v>324</v>
       </c>
@@ -15637,7 +15826,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="533" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533" s="6" t="s">
         <v>492</v>
       </c>
@@ -15658,7 +15847,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="534" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534" s="6" t="s">
         <v>493</v>
       </c>
@@ -15670,7 +15859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535" s="6" t="s">
         <v>494</v>
       </c>
@@ -15691,7 +15880,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="536" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536" s="6" t="s">
         <v>495</v>
       </c>
@@ -15712,7 +15901,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="537" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537" s="6" t="s">
         <v>375</v>
       </c>
@@ -15733,7 +15922,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="538" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538" s="6" t="s">
         <v>109</v>
       </c>
@@ -15751,7 +15940,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="539" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539" s="6" t="s">
         <v>496</v>
       </c>
@@ -15769,7 +15958,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="540" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540" s="6" t="s">
         <v>135</v>
       </c>
@@ -15790,7 +15979,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="541" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541" s="6" t="s">
         <v>332</v>
       </c>
@@ -15811,7 +16000,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="542" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542" s="6" t="s">
         <v>75</v>
       </c>
@@ -15832,7 +16021,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="543" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543" s="6" t="s">
         <v>497</v>
       </c>
@@ -15853,7 +16042,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="544" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544" s="6" t="s">
         <v>121</v>
       </c>
@@ -15871,7 +16060,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="545" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545" s="6" t="s">
         <v>498</v>
       </c>
@@ -15883,7 +16072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="546" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546" s="6" t="s">
         <v>499</v>
       </c>
@@ -15901,7 +16090,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="547" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547" s="6" t="s">
         <v>500</v>
       </c>
@@ -15922,7 +16111,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="548" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548" s="6" t="s">
         <v>117</v>
       </c>
@@ -15943,7 +16132,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="549" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549" s="6" t="s">
         <v>243</v>
       </c>
@@ -15964,7 +16153,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="550" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550" s="6" t="s">
         <v>501</v>
       </c>
@@ -15982,7 +16171,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="551" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551" s="6" t="s">
         <v>502</v>
       </c>
@@ -16000,7 +16189,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="552" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552" s="6" t="s">
         <v>503</v>
       </c>
@@ -16018,7 +16207,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="553" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553" s="6" t="s">
         <v>504</v>
       </c>
@@ -16036,7 +16225,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="554" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554" s="6" t="s">
         <v>505</v>
       </c>
@@ -16048,7 +16237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="555" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555" s="6" t="s">
         <v>315</v>
       </c>
@@ -16069,7 +16258,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="556" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556" s="6" t="s">
         <v>506</v>
       </c>
@@ -16090,7 +16279,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="557" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557" s="6" t="s">
         <v>304</v>
       </c>
@@ -16111,7 +16300,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="558" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558" s="6" t="s">
         <v>507</v>
       </c>
@@ -16123,7 +16312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559" s="6" t="s">
         <v>508</v>
       </c>
@@ -16144,7 +16333,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="560" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560" s="6" t="s">
         <v>509</v>
       </c>
@@ -16156,7 +16345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561" s="6" t="s">
         <v>510</v>
       </c>
@@ -16174,7 +16363,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="562" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562" s="6" t="s">
         <v>123</v>
       </c>
@@ -16195,7 +16384,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="563" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563" s="6" t="s">
         <v>511</v>
       </c>
@@ -16213,7 +16402,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="564" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564" s="6" t="s">
         <v>512</v>
       </c>
@@ -16234,7 +16423,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="565" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565" s="6" t="s">
         <v>513</v>
       </c>
@@ -16255,7 +16444,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="566" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566" s="6" t="s">
         <v>514</v>
       </c>
@@ -16276,7 +16465,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="567" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567" s="6" t="s">
         <v>515</v>
       </c>
@@ -16288,7 +16477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568" s="6" t="s">
         <v>516</v>
       </c>
@@ -16300,7 +16489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569" s="6" t="s">
         <v>517</v>
       </c>
@@ -16312,7 +16501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570" s="6" t="s">
         <v>518</v>
       </c>
@@ -16333,7 +16522,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="571" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571" s="6" t="s">
         <v>519</v>
       </c>
@@ -16345,7 +16534,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572" s="6" t="s">
         <v>54</v>
       </c>
@@ -16366,7 +16555,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="573" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573" s="6" t="s">
         <v>122</v>
       </c>
@@ -16387,7 +16576,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="574" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574" s="6" t="s">
         <v>199</v>
       </c>
@@ -16408,7 +16597,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="575" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575" s="6" t="s">
         <v>520</v>
       </c>
@@ -16420,7 +16609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="576" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576" s="6" t="s">
         <v>521</v>
       </c>
@@ -16432,7 +16621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577" s="6" t="s">
         <v>258</v>
       </c>
@@ -16453,7 +16642,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="578" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578" s="6" t="s">
         <v>522</v>
       </c>
@@ -16474,7 +16663,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="579" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579" s="6" t="s">
         <v>523</v>
       </c>
@@ -16482,7 +16671,7 @@
         <v>794</v>
       </c>
       <c r="C579" s="1" t="b">
-        <f t="shared" ref="C579:C642" si="9">ISNUMBER(SEARCH("trimethylsilyl",A579))</f>
+        <f t="shared" ref="C579:C642" si="9">ISNUMBER(SEARCH("silyl",A579))</f>
         <v>0</v>
       </c>
       <c r="D579">
@@ -16492,7 +16681,7 @@
         <v>1215</v>
       </c>
     </row>
-    <row r="580" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580" s="6" t="s">
         <v>524</v>
       </c>
@@ -16513,7 +16702,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="581" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581" s="6" t="s">
         <v>525</v>
       </c>
@@ -16534,7 +16723,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="582" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582" s="6" t="s">
         <v>74</v>
       </c>
@@ -16552,7 +16741,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="583" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583" s="6" t="s">
         <v>140</v>
       </c>
@@ -16573,7 +16762,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="584" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584" s="6" t="s">
         <v>526</v>
       </c>
@@ -16594,7 +16783,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="585" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585" s="6" t="s">
         <v>527</v>
       </c>
@@ -16615,7 +16804,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="586" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586" s="6" t="s">
         <v>276</v>
       </c>
@@ -16636,7 +16825,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="587" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587" s="6" t="s">
         <v>528</v>
       </c>
@@ -16657,7 +16846,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="588" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588" s="6" t="s">
         <v>529</v>
       </c>
@@ -16675,7 +16864,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="589" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589" s="6" t="s">
         <v>530</v>
       </c>
@@ -16687,7 +16876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="590" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590" s="6" t="s">
         <v>531</v>
       </c>
@@ -16708,7 +16897,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="591" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591" s="6" t="s">
         <v>532</v>
       </c>
@@ -16729,7 +16918,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="592" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592" s="6" t="s">
         <v>533</v>
       </c>
@@ -16741,7 +16930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="593" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593" s="6" t="s">
         <v>534</v>
       </c>
@@ -16762,7 +16951,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="594" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594" s="6" t="s">
         <v>535</v>
       </c>
@@ -16783,7 +16972,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="595" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595" s="6" t="s">
         <v>536</v>
       </c>
@@ -16804,7 +16993,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="596" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596" s="6" t="s">
         <v>139</v>
       </c>
@@ -16825,7 +17014,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="597" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597" s="6" t="s">
         <v>339</v>
       </c>
@@ -16846,7 +17035,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="598" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598" s="6" t="s">
         <v>537</v>
       </c>
@@ -16867,7 +17056,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="599" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599" s="7" t="s">
         <v>539</v>
       </c>
@@ -16894,7 +17083,7 @@
       </c>
       <c r="C600" s="1" t="b">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D600">
         <v>91742919</v>
@@ -16903,7 +17092,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="601" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601" s="7" t="s">
         <v>541</v>
       </c>
@@ -16921,7 +17110,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="602" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602" s="7" t="s">
         <v>38</v>
       </c>
@@ -16933,7 +17122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="603" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603" s="7" t="s">
         <v>542</v>
       </c>
@@ -16951,7 +17140,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="604" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604" s="7" t="s">
         <v>543</v>
       </c>
@@ -16969,7 +17158,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="605" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605" s="7" t="s">
         <v>544</v>
       </c>
@@ -16987,7 +17176,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="606" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A606" s="7" t="s">
         <v>545</v>
       </c>
@@ -17023,7 +17212,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="608" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A608" s="7" t="s">
         <v>547</v>
       </c>
@@ -17041,7 +17230,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="609" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A609" s="7" t="s">
         <v>548</v>
       </c>
@@ -17062,7 +17251,7 @@
       </c>
       <c r="C610" s="1" t="b">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D610">
         <v>91716313</v>
@@ -17071,7 +17260,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="611" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A611" s="7" t="s">
         <v>550</v>
       </c>
@@ -17083,7 +17272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="612" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A612" s="7" t="s">
         <v>551</v>
       </c>
@@ -17101,7 +17290,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="613" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A613" s="7" t="s">
         <v>552</v>
       </c>
@@ -17137,7 +17326,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="615" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A615" s="7" t="s">
         <v>554</v>
       </c>
@@ -17149,7 +17338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="616" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A616" s="7" t="s">
         <v>555</v>
       </c>
@@ -17167,7 +17356,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="617" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A617" s="7" t="s">
         <v>556</v>
       </c>
@@ -17179,7 +17368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="618" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A618" s="7" t="s">
         <v>557</v>
       </c>
@@ -17197,7 +17386,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="619" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A619" s="7" t="s">
         <v>558</v>
       </c>
@@ -17215,7 +17404,7 @@
         <v>1243</v>
       </c>
     </row>
-    <row r="620" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A620" s="7" t="s">
         <v>559</v>
       </c>
@@ -17227,7 +17416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="621" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A621" s="7" t="s">
         <v>560</v>
       </c>
@@ -17248,7 +17437,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="622" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A622" s="7" t="s">
         <v>561</v>
       </c>
@@ -17266,7 +17455,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A623" s="7" t="s">
         <v>562</v>
       </c>
@@ -17284,7 +17473,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A624" s="7" t="s">
         <v>384</v>
       </c>
@@ -17305,7 +17494,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="625" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A625" s="7" t="s">
         <v>57</v>
       </c>
@@ -17344,7 +17533,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="627" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A627" s="7" t="s">
         <v>564</v>
       </c>
@@ -17356,7 +17545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" s="7" t="s">
         <v>565</v>
       </c>
@@ -17368,7 +17557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="629" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" s="7" t="s">
         <v>566</v>
       </c>
@@ -17386,7 +17575,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="630" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" s="7" t="s">
         <v>567</v>
       </c>
@@ -17404,7 +17593,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="631" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" s="7" t="s">
         <v>568</v>
       </c>
@@ -17443,7 +17632,7 @@
         <v>1251</v>
       </c>
     </row>
-    <row r="633" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" s="7" t="s">
         <v>570</v>
       </c>
@@ -17464,7 +17653,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="634" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" s="7" t="s">
         <v>571</v>
       </c>
@@ -17482,7 +17671,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="635" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="7" t="s">
         <v>572</v>
       </c>
@@ -17500,7 +17689,7 @@
         <v>1254</v>
       </c>
     </row>
-    <row r="636" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" s="7" t="s">
         <v>573</v>
       </c>
@@ -17518,7 +17707,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="637" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" s="7" t="s">
         <v>574</v>
       </c>
@@ -17539,7 +17728,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="638" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A638" s="7" t="s">
         <v>575</v>
       </c>
@@ -17557,7 +17746,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="639" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A639" s="7" t="s">
         <v>451</v>
       </c>
@@ -17578,7 +17767,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="640" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A640" s="7" t="s">
         <v>576</v>
       </c>
@@ -17599,7 +17788,7 @@
       </c>
       <c r="C641" s="1" t="b">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D641">
         <v>91741551</v>
@@ -17608,7 +17797,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="642" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A642" s="7" t="s">
         <v>501</v>
       </c>
@@ -17626,7 +17815,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="643" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A643" s="7" t="s">
         <v>107</v>
       </c>
@@ -17634,7 +17823,7 @@
         <v>1430</v>
       </c>
       <c r="C643" s="1" t="b">
-        <f t="shared" ref="C643:C706" si="10">ISNUMBER(SEARCH("trimethylsilyl",A643))</f>
+        <f t="shared" ref="C643:C706" si="10">ISNUMBER(SEARCH("silyl",A643))</f>
         <v>0</v>
       </c>
       <c r="D643">
@@ -17644,7 +17833,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="644" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A644" s="7" t="s">
         <v>109</v>
       </c>
@@ -17662,7 +17851,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="645" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A645" s="7" t="s">
         <v>578</v>
       </c>
@@ -17680,7 +17869,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="646" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A646" s="7" t="s">
         <v>579</v>
       </c>
@@ -17698,7 +17887,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="647" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A647" s="7" t="s">
         <v>79</v>
       </c>
@@ -17716,7 +17905,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="648" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A648" s="7" t="s">
         <v>580</v>
       </c>
@@ -17734,7 +17923,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="649" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A649" s="7" t="s">
         <v>581</v>
       </c>
@@ -17752,7 +17941,7 @@
         <v>1262</v>
       </c>
     </row>
-    <row r="650" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A650" s="7" t="s">
         <v>582</v>
       </c>
@@ -17773,7 +17962,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="651" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A651" s="7" t="s">
         <v>583</v>
       </c>
@@ -17791,7 +17980,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="652" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A652" s="7" t="s">
         <v>584</v>
       </c>
@@ -17809,7 +17998,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="653" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A653" s="7" t="s">
         <v>585</v>
       </c>
@@ -17839,10 +18028,10 @@
       </c>
       <c r="C654" s="1" t="b">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="655" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="655" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A655" s="7" t="s">
         <v>587</v>
       </c>
@@ -17863,7 +18052,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="656" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A656" s="7" t="s">
         <v>588</v>
       </c>
@@ -17881,7 +18070,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="657" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A657" s="7" t="s">
         <v>589</v>
       </c>
@@ -17893,7 +18082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="658" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A658" s="7" t="s">
         <v>590</v>
       </c>
@@ -17914,7 +18103,7 @@
         <v>1269</v>
       </c>
     </row>
-    <row r="659" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A659" s="7" t="s">
         <v>591</v>
       </c>
@@ -17935,7 +18124,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="660" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A660" s="7" t="s">
         <v>592</v>
       </c>
@@ -17953,7 +18142,7 @@
         <v>1271</v>
       </c>
     </row>
-    <row r="661" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A661" s="7" t="s">
         <v>380</v>
       </c>
@@ -17974,7 +18163,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="662" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A662" s="7" t="s">
         <v>593</v>
       </c>
@@ -17995,7 +18184,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="663" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A663" s="7" t="s">
         <v>594</v>
       </c>
@@ -18013,7 +18202,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="664" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A664" s="7" t="s">
         <v>84</v>
       </c>
@@ -18034,7 +18223,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="665" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A665" s="7" t="s">
         <v>595</v>
       </c>
@@ -18055,7 +18244,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="666" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A666" s="7" t="s">
         <v>596</v>
       </c>
@@ -18073,7 +18262,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="667" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A667" s="7" t="s">
         <v>597</v>
       </c>
@@ -18091,7 +18280,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="668" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A668" s="7" t="s">
         <v>88</v>
       </c>
@@ -18112,7 +18301,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="669" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A669" s="7" t="s">
         <v>598</v>
       </c>
@@ -18130,7 +18319,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="670" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A670" s="7" t="s">
         <v>91</v>
       </c>
@@ -18148,7 +18337,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="671" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A671" s="7" t="s">
         <v>599</v>
       </c>
@@ -18166,7 +18355,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="672" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A672" s="7" t="s">
         <v>600</v>
       </c>
@@ -18187,7 +18376,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="673" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A673" s="7" t="s">
         <v>601</v>
       </c>
@@ -18208,10 +18397,10 @@
       </c>
       <c r="C674" s="1" t="b">
         <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="675" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="675" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A675" s="7" t="s">
         <v>95</v>
       </c>
@@ -18232,7 +18421,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="676" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A676" s="7" t="s">
         <v>603</v>
       </c>
@@ -18259,7 +18448,7 @@
       </c>
       <c r="C677" s="1" t="b">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D677">
         <v>554546</v>
@@ -18268,7 +18457,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="678" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A678" s="7" t="s">
         <v>605</v>
       </c>
@@ -18289,7 +18478,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="679" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A679" s="7" t="s">
         <v>606</v>
       </c>
@@ -18307,7 +18496,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="680" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A680" s="7" t="s">
         <v>607</v>
       </c>
@@ -18328,7 +18517,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="681" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A681" s="7" t="s">
         <v>608</v>
       </c>
@@ -18349,7 +18538,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="682" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A682" s="7" t="s">
         <v>609</v>
       </c>
@@ -18367,7 +18556,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="683" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A683" s="7" t="s">
         <v>610</v>
       </c>
@@ -18385,7 +18574,7 @@
         <v>1286</v>
       </c>
     </row>
-    <row r="684" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A684" s="7" t="s">
         <v>611</v>
       </c>
@@ -18415,7 +18604,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="686" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A686" s="7" t="s">
         <v>613</v>
       </c>
@@ -18436,7 +18625,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="687" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A687" s="7" t="s">
         <v>614</v>
       </c>
@@ -18457,7 +18646,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="688" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A688" s="7" t="s">
         <v>615</v>
       </c>
@@ -18487,7 +18676,7 @@
       </c>
       <c r="C689" s="1" t="b">
         <f t="shared" si="10"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D689">
         <v>10357235</v>
@@ -18496,7 +18685,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="690" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A690" s="7" t="s">
         <v>617</v>
       </c>
@@ -18517,7 +18706,7 @@
         <v>1292</v>
       </c>
     </row>
-    <row r="691" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A691" s="7" t="s">
         <v>618</v>
       </c>
@@ -18535,7 +18724,7 @@
         <v>1293</v>
       </c>
     </row>
-    <row r="692" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A692" s="7" t="s">
         <v>619</v>
       </c>
@@ -18556,7 +18745,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="693" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A693" s="7" t="s">
         <v>462</v>
       </c>
@@ -18577,7 +18766,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="694" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A694" s="7" t="s">
         <v>620</v>
       </c>
@@ -18598,7 +18787,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A695" s="7" t="s">
         <v>621</v>
       </c>
@@ -18634,7 +18823,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="697" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A697" s="7" t="s">
         <v>623</v>
       </c>
@@ -18655,7 +18844,7 @@
         <v>1298</v>
       </c>
     </row>
-    <row r="698" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A698" s="7" t="s">
         <v>624</v>
       </c>
@@ -18673,7 +18862,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="699" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A699" s="7" t="s">
         <v>625</v>
       </c>
@@ -18691,7 +18880,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="700" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A700" s="7" t="s">
         <v>626</v>
       </c>
@@ -18709,7 +18898,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="701" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A701" s="7" t="s">
         <v>627</v>
       </c>
@@ -18727,7 +18916,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="702" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A702" s="7" t="s">
         <v>628</v>
       </c>
@@ -18739,7 +18928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="703" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A703" s="7" t="s">
         <v>629</v>
       </c>
@@ -18760,7 +18949,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="704" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A704" s="7" t="s">
         <v>139</v>
       </c>
@@ -18781,7 +18970,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="705" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A705" s="7" t="s">
         <v>630</v>
       </c>
@@ -18802,7 +18991,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="706" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A706" s="7" t="s">
         <v>631</v>
       </c>
@@ -18814,7 +19003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="707" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A707" s="7" t="s">
         <v>632</v>
       </c>
@@ -18822,7 +19011,7 @@
         <v>1430</v>
       </c>
       <c r="C707" s="1" t="b">
-        <f t="shared" ref="C707:C770" si="11">ISNUMBER(SEARCH("trimethylsilyl",A707))</f>
+        <f t="shared" ref="C707:C770" si="11">ISNUMBER(SEARCH("silyl",A707))</f>
         <v>0</v>
       </c>
       <c r="D707">
@@ -18835,7 +19024,7 @@
         <v>1305</v>
       </c>
     </row>
-    <row r="708" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A708" s="7" t="s">
         <v>633</v>
       </c>
@@ -18853,7 +19042,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="709" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A709" s="7" t="s">
         <v>634</v>
       </c>
@@ -18871,7 +19060,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="710" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A710" s="7" t="s">
         <v>635</v>
       </c>
@@ -18889,7 +19078,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="711" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A711" s="7" t="s">
         <v>142</v>
       </c>
@@ -18910,7 +19099,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="712" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A712" s="7" t="s">
         <v>636</v>
       </c>
@@ -18928,7 +19117,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="713" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A713" s="7" t="s">
         <v>637</v>
       </c>
@@ -18955,7 +19144,7 @@
       </c>
       <c r="C714" s="1" t="b">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D714">
         <v>91697308</v>
@@ -18964,7 +19153,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="715" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A715" s="7" t="s">
         <v>639</v>
       </c>
@@ -18982,7 +19171,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="716" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A716" s="7" t="s">
         <v>640</v>
       </c>
@@ -19000,7 +19189,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="717" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A717" s="7" t="s">
         <v>641</v>
       </c>
@@ -19027,10 +19216,10 @@
       </c>
       <c r="C718" s="1" t="b">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="719" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="719" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A719" s="7" t="s">
         <v>491</v>
       </c>
@@ -19051,7 +19240,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="720" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A720" s="7" t="s">
         <v>150</v>
       </c>
@@ -19081,10 +19270,10 @@
       </c>
       <c r="C721" s="1" t="b">
         <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="722" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="722" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A722" s="7" t="s">
         <v>644</v>
       </c>
@@ -19102,7 +19291,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="723" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A723" s="7" t="s">
         <v>645</v>
       </c>
@@ -19123,7 +19312,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="724" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A724" s="7" t="s">
         <v>646</v>
       </c>
@@ -19141,7 +19330,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="725" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A725" s="7" t="s">
         <v>647</v>
       </c>
@@ -19159,7 +19348,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="726" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A726" s="7" t="s">
         <v>648</v>
       </c>
@@ -19177,7 +19366,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="727" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A727" s="7" t="s">
         <v>649</v>
       </c>
@@ -19195,7 +19384,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="728" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A728" s="7" t="s">
         <v>650</v>
       </c>
@@ -19213,7 +19402,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="729" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A729" s="7" t="s">
         <v>651</v>
       </c>
@@ -19231,7 +19420,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="730" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A730" s="7" t="s">
         <v>652</v>
       </c>
@@ -19261,7 +19450,7 @@
         <v>1322</v>
       </c>
     </row>
-    <row r="732" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A732" s="7" t="s">
         <v>654</v>
       </c>
@@ -19279,7 +19468,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="733" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A733" s="7" t="s">
         <v>655</v>
       </c>
@@ -19297,7 +19486,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="734" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A734" s="7" t="s">
         <v>656</v>
       </c>
@@ -19318,7 +19507,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="735" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A735" s="7" t="s">
         <v>159</v>
       </c>
@@ -19339,7 +19528,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="736" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A736" s="7" t="s">
         <v>450</v>
       </c>
@@ -19360,7 +19549,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="737" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A737" s="7" t="s">
         <v>657</v>
       </c>
@@ -19381,7 +19570,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="738" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A738" s="7" t="s">
         <v>658</v>
       </c>
@@ -19402,7 +19591,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="739" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A739" s="7" t="s">
         <v>160</v>
       </c>
@@ -19423,7 +19612,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="740" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A740" s="7" t="s">
         <v>659</v>
       </c>
@@ -19444,7 +19633,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="741" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A741" s="7" t="s">
         <v>161</v>
       </c>
@@ -19462,7 +19651,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="742" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A742" s="7" t="s">
         <v>660</v>
       </c>
@@ -19483,7 +19672,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="743" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A743" s="7" t="s">
         <v>661</v>
       </c>
@@ -19504,7 +19693,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="744" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A744" s="7" t="s">
         <v>531</v>
       </c>
@@ -19525,7 +19714,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="745" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A745" s="7" t="s">
         <v>662</v>
       </c>
@@ -19537,7 +19726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="746" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A746" s="7" t="s">
         <v>663</v>
       </c>
@@ -19549,7 +19738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="747" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A747" s="7" t="s">
         <v>664</v>
       </c>
@@ -19567,7 +19756,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="748" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A748" s="7" t="s">
         <v>665</v>
       </c>
@@ -19579,7 +19768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="749" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A749" s="7" t="s">
         <v>666</v>
       </c>
@@ -19591,7 +19780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="750" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A750" s="7" t="s">
         <v>667</v>
       </c>
@@ -19603,7 +19792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="751" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A751" s="7" t="s">
         <v>668</v>
       </c>
@@ -19615,7 +19804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="752" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A752" s="7" t="s">
         <v>180</v>
       </c>
@@ -19636,7 +19825,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="753" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A753" s="7" t="s">
         <v>669</v>
       </c>
@@ -19657,7 +19846,7 @@
         <v>1331</v>
       </c>
     </row>
-    <row r="754" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A754" s="7" t="s">
         <v>670</v>
       </c>
@@ -19669,7 +19858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="755" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A755" s="7" t="s">
         <v>671</v>
       </c>
@@ -19687,7 +19876,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="756" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A756" s="7" t="s">
         <v>184</v>
       </c>
@@ -19708,7 +19897,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="757" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A757" s="7" t="s">
         <v>406</v>
       </c>
@@ -19729,7 +19918,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="758" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A758" s="7" t="s">
         <v>186</v>
       </c>
@@ -19750,7 +19939,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="759" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A759" s="7" t="s">
         <v>187</v>
       </c>
@@ -19771,7 +19960,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="760" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A760" s="7" t="s">
         <v>672</v>
       </c>
@@ -19792,7 +19981,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="761" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A761" s="7" t="s">
         <v>673</v>
       </c>
@@ -19804,7 +19993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="762" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A762" s="7" t="s">
         <v>527</v>
       </c>
@@ -19825,7 +20014,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="763" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A763" s="7" t="s">
         <v>674</v>
       </c>
@@ -19843,7 +20032,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="764" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A764" s="7" t="s">
         <v>675</v>
       </c>
@@ -19864,7 +20053,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="765" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A765" s="7" t="s">
         <v>676</v>
       </c>
@@ -19882,7 +20071,7 @@
         <v>1336</v>
       </c>
     </row>
-    <row r="766" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A766" s="7" t="s">
         <v>199</v>
       </c>
@@ -19903,7 +20092,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="767" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A767" s="7" t="s">
         <v>677</v>
       </c>
@@ -19924,7 +20113,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="768" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A768" s="7" t="s">
         <v>678</v>
       </c>
@@ -19945,7 +20134,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="769" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A769" s="7" t="s">
         <v>679</v>
       </c>
@@ -19966,7 +20155,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="770" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A770" s="7" t="s">
         <v>680</v>
       </c>
@@ -19987,7 +20176,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="771" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A771" s="7" t="s">
         <v>681</v>
       </c>
@@ -19995,7 +20184,7 @@
         <v>1430</v>
       </c>
       <c r="C771" s="1" t="b">
-        <f t="shared" ref="C771:C834" si="12">ISNUMBER(SEARCH("trimethylsilyl",A771))</f>
+        <f t="shared" ref="C771:C834" si="12">ISNUMBER(SEARCH("silyl",A771))</f>
         <v>0</v>
       </c>
       <c r="D771">
@@ -20005,7 +20194,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="772" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A772" s="7" t="s">
         <v>682</v>
       </c>
@@ -20026,7 +20215,7 @@
         <v>1342</v>
       </c>
     </row>
-    <row r="773" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A773" s="7" t="s">
         <v>683</v>
       </c>
@@ -20044,7 +20233,7 @@
         <v>1343</v>
       </c>
     </row>
-    <row r="774" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A774" s="7" t="s">
         <v>684</v>
       </c>
@@ -20062,7 +20251,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="775" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A775" s="7" t="s">
         <v>685</v>
       </c>
@@ -20080,7 +20269,7 @@
         <v>1345</v>
       </c>
     </row>
-    <row r="776" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A776" s="7" t="s">
         <v>686</v>
       </c>
@@ -20110,10 +20299,10 @@
       </c>
       <c r="C777" s="1" t="b">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="778" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="778" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A778" s="7" t="s">
         <v>688</v>
       </c>
@@ -20125,7 +20314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="779" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A779" s="7" t="s">
         <v>689</v>
       </c>
@@ -20143,7 +20332,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="780" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A780" s="7" t="s">
         <v>690</v>
       </c>
@@ -20161,7 +20350,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="781" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A781" s="7" t="s">
         <v>691</v>
       </c>
@@ -20182,7 +20371,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="782" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A782" s="7" t="s">
         <v>692</v>
       </c>
@@ -20203,7 +20392,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="783" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A783" s="7" t="s">
         <v>233</v>
       </c>
@@ -20224,7 +20413,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="784" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A784" s="7" t="s">
         <v>693</v>
       </c>
@@ -20245,7 +20434,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="785" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A785" s="7" t="s">
         <v>694</v>
       </c>
@@ -20266,7 +20455,7 @@
         <v>1351</v>
       </c>
     </row>
-    <row r="786" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A786" s="7" t="s">
         <v>240</v>
       </c>
@@ -20287,7 +20476,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="787" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A787" s="7" t="s">
         <v>695</v>
       </c>
@@ -20305,7 +20494,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="788" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A788" s="7" t="s">
         <v>696</v>
       </c>
@@ -20326,7 +20515,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="789" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A789" s="7" t="s">
         <v>465</v>
       </c>
@@ -20347,7 +20536,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="790" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A790" s="7" t="s">
         <v>246</v>
       </c>
@@ -20368,7 +20557,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="791" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A791" s="7" t="s">
         <v>697</v>
       </c>
@@ -20389,7 +20578,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="792" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A792" s="7" t="s">
         <v>698</v>
       </c>
@@ -20407,7 +20596,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="793" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A793" s="7" t="s">
         <v>699</v>
       </c>
@@ -20425,7 +20614,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="794" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A794" s="7" t="s">
         <v>254</v>
       </c>
@@ -20443,7 +20632,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="795" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A795" s="7" t="s">
         <v>518</v>
       </c>
@@ -20464,7 +20653,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="796" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A796" s="7" t="s">
         <v>255</v>
       </c>
@@ -20494,10 +20683,10 @@
       </c>
       <c r="C797" s="1" t="b">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="798" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="798" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A798" s="7" t="s">
         <v>258</v>
       </c>
@@ -20518,7 +20707,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="799" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A799" s="7" t="s">
         <v>701</v>
       </c>
@@ -20536,7 +20725,7 @@
         <v>1357</v>
       </c>
     </row>
-    <row r="800" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A800" s="7" t="s">
         <v>702</v>
       </c>
@@ -20557,7 +20746,7 @@
         <v>1080</v>
       </c>
     </row>
-    <row r="801" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A801" s="7" t="s">
         <v>703</v>
       </c>
@@ -20578,7 +20767,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="802" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A802" s="7" t="s">
         <v>704</v>
       </c>
@@ -20596,7 +20785,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="803" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A803" s="7" t="s">
         <v>525</v>
       </c>
@@ -20617,7 +20806,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="804" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A804" s="7" t="s">
         <v>263</v>
       </c>
@@ -20638,7 +20827,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="805" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A805" s="7" t="s">
         <v>265</v>
       </c>
@@ -20659,7 +20848,7 @@
         <v>1004</v>
       </c>
     </row>
-    <row r="806" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A806" s="7" t="s">
         <v>705</v>
       </c>
@@ -20689,7 +20878,7 @@
       </c>
       <c r="C807" s="1" t="b">
         <f t="shared" si="12"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D807">
         <v>19104051</v>
@@ -20698,7 +20887,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="808" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A808" s="7" t="s">
         <v>707</v>
       </c>
@@ -20716,7 +20905,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="809" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A809" s="7" t="s">
         <v>708</v>
       </c>
@@ -20737,7 +20926,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="810" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A810" s="7" t="s">
         <v>709</v>
       </c>
@@ -20758,7 +20947,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="811" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A811" s="7" t="s">
         <v>710</v>
       </c>
@@ -20779,7 +20968,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="812" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A812" s="7" t="s">
         <v>537</v>
       </c>
@@ -20800,7 +20989,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="813" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A813" s="7" t="s">
         <v>273</v>
       </c>
@@ -20821,7 +21010,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="814" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A814" s="7" t="s">
         <v>711</v>
       </c>
@@ -20842,7 +21031,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="815" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A815" s="7" t="s">
         <v>712</v>
       </c>
@@ -20860,7 +21049,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="816" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A816" s="7" t="s">
         <v>276</v>
       </c>
@@ -20890,10 +21079,10 @@
       </c>
       <c r="C817" s="1" t="b">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="818" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="818" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A818" s="7" t="s">
         <v>714</v>
       </c>
@@ -20911,7 +21100,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="819" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A819" s="7" t="s">
         <v>715</v>
       </c>
@@ -20929,7 +21118,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="820" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A820" s="7" t="s">
         <v>278</v>
       </c>
@@ -20950,7 +21139,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="821" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A821" s="7" t="s">
         <v>279</v>
       </c>
@@ -20971,7 +21160,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="822" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A822" s="7" t="s">
         <v>716</v>
       </c>
@@ -20992,7 +21181,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="823" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A823" s="7" t="s">
         <v>717</v>
       </c>
@@ -21013,7 +21202,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="824" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A824" s="7" t="s">
         <v>294</v>
       </c>
@@ -21034,7 +21223,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="825" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A825" s="7" t="s">
         <v>282</v>
       </c>
@@ -21055,7 +21244,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="826" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A826" s="7" t="s">
         <v>528</v>
       </c>
@@ -21085,10 +21274,10 @@
       </c>
       <c r="C827" s="1" t="b">
         <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="828" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="828" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A828" s="7" t="s">
         <v>470</v>
       </c>
@@ -21109,7 +21298,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="829" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A829" s="7" t="s">
         <v>286</v>
       </c>
@@ -21130,7 +21319,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="830" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A830" s="7" t="s">
         <v>719</v>
       </c>
@@ -21148,7 +21337,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="831" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A831" s="7" t="s">
         <v>720</v>
       </c>
@@ -21169,7 +21358,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="832" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A832" s="7" t="s">
         <v>288</v>
       </c>
@@ -21190,7 +21379,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="833" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A833" s="7" t="s">
         <v>721</v>
       </c>
@@ -21208,7 +21397,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="834" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A834" s="7" t="s">
         <v>722</v>
       </c>
@@ -21229,7 +21418,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="835" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A835" s="7" t="s">
         <v>723</v>
       </c>
@@ -21237,7 +21426,7 @@
         <v>1430</v>
       </c>
       <c r="C835" s="1" t="b">
-        <f t="shared" ref="C835:C898" si="13">ISNUMBER(SEARCH("trimethylsilyl",A835))</f>
+        <f t="shared" ref="C835:C898" si="13">ISNUMBER(SEARCH("silyl",A835))</f>
         <v>0</v>
       </c>
       <c r="D835">
@@ -21250,7 +21439,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="836" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A836" s="7" t="s">
         <v>398</v>
       </c>
@@ -21271,7 +21460,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="837" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A837" s="7" t="s">
         <v>404</v>
       </c>
@@ -21292,7 +21481,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="838" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A838" s="7" t="s">
         <v>290</v>
       </c>
@@ -21313,7 +21502,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="839" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A839" s="7" t="s">
         <v>370</v>
       </c>
@@ -21334,7 +21523,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="840" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A840" s="7" t="s">
         <v>724</v>
       </c>
@@ -21352,7 +21541,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="841" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A841" s="7" t="s">
         <v>725</v>
       </c>
@@ -21373,7 +21562,7 @@
         <v>1374</v>
       </c>
     </row>
-    <row r="842" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A842" s="7" t="s">
         <v>392</v>
       </c>
@@ -21394,7 +21583,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="843" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A843" s="7" t="s">
         <v>726</v>
       </c>
@@ -21412,7 +21601,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="844" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A844" s="7" t="s">
         <v>295</v>
       </c>
@@ -21430,7 +21619,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="845" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A845" s="7" t="s">
         <v>727</v>
       </c>
@@ -21451,7 +21640,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="846" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A846" s="7" t="s">
         <v>728</v>
       </c>
@@ -21472,7 +21661,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="847" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A847" s="7" t="s">
         <v>729</v>
       </c>
@@ -21490,7 +21679,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="848" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A848" s="7" t="s">
         <v>390</v>
       </c>
@@ -21508,7 +21697,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="849" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A849" s="7" t="s">
         <v>730</v>
       </c>
@@ -21526,7 +21715,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="850" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A850" s="7" t="s">
         <v>731</v>
       </c>
@@ -21544,7 +21733,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="851" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A851" s="7" t="s">
         <v>732</v>
       </c>
@@ -21562,7 +21751,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="852" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A852" s="7" t="s">
         <v>733</v>
       </c>
@@ -21583,7 +21772,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="853" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A853" s="7" t="s">
         <v>304</v>
       </c>
@@ -21604,7 +21793,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="854" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A854" s="7" t="s">
         <v>734</v>
       </c>
@@ -21625,7 +21814,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="855" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A855" s="7" t="s">
         <v>735</v>
       </c>
@@ -21643,7 +21832,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="856" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A856" s="7" t="s">
         <v>736</v>
       </c>
@@ -21655,7 +21844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="857" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A857" s="7" t="s">
         <v>737</v>
       </c>
@@ -21676,7 +21865,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="858" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A858" s="7" t="s">
         <v>738</v>
       </c>
@@ -21697,7 +21886,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="859" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A859" s="7" t="s">
         <v>739</v>
       </c>
@@ -21709,7 +21898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="860" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A860" s="7" t="s">
         <v>740</v>
       </c>
@@ -21727,7 +21916,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="861" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A861" s="7" t="s">
         <v>741</v>
       </c>
@@ -21748,7 +21937,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="862" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A862" s="7" t="s">
         <v>742</v>
       </c>
@@ -21766,7 +21955,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="863" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A863" s="7" t="s">
         <v>315</v>
       </c>
@@ -21787,7 +21976,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="864" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A864" s="7" t="s">
         <v>316</v>
       </c>
@@ -21808,7 +21997,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="865" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A865" s="7" t="s">
         <v>306</v>
       </c>
@@ -21847,7 +22036,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="867" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A867" s="7" t="s">
         <v>744</v>
       </c>
@@ -21865,7 +22054,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="868" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A868" s="7" t="s">
         <v>506</v>
       </c>
@@ -21886,7 +22075,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="869" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A869" s="7" t="s">
         <v>745</v>
       </c>
@@ -21904,7 +22093,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="870" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A870" s="7" t="s">
         <v>320</v>
       </c>
@@ -21937,7 +22126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="872" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A872" s="7" t="s">
         <v>747</v>
       </c>
@@ -21958,7 +22147,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="873" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A873" s="7" t="s">
         <v>748</v>
       </c>
@@ -21976,7 +22165,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="874" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A874" s="7" t="s">
         <v>749</v>
       </c>
@@ -21997,7 +22186,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="875" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A875" s="7" t="s">
         <v>324</v>
       </c>
@@ -22018,7 +22207,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="876" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A876" s="7" t="s">
         <v>325</v>
       </c>
@@ -22039,7 +22228,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="877" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A877" s="7" t="s">
         <v>750</v>
       </c>
@@ -22060,7 +22249,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="878" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A878" s="7" t="s">
         <v>751</v>
       </c>
@@ -22081,7 +22270,7 @@
         <v>1394</v>
       </c>
     </row>
-    <row r="879" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A879" s="7" t="s">
         <v>752</v>
       </c>
@@ -22102,7 +22291,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="880" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A880" s="7" t="s">
         <v>328</v>
       </c>
@@ -22123,7 +22312,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="881" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A881" s="7" t="s">
         <v>753</v>
       </c>
@@ -22159,7 +22348,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="883" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A883" s="7" t="s">
         <v>332</v>
       </c>
@@ -22180,7 +22369,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="884" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A884" s="7" t="s">
         <v>479</v>
       </c>
@@ -22201,7 +22390,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="885" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A885" s="7" t="s">
         <v>417</v>
       </c>
@@ -22222,7 +22411,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="886" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A886" s="7" t="s">
         <v>446</v>
       </c>
@@ -22243,7 +22432,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="887" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A887" s="7" t="s">
         <v>755</v>
       </c>
@@ -22261,7 +22450,7 @@
         <v>1398</v>
       </c>
     </row>
-    <row r="888" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A888" s="7" t="s">
         <v>389</v>
       </c>
@@ -22282,7 +22471,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="889" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A889" s="7" t="s">
         <v>756</v>
       </c>
@@ -22303,7 +22492,7 @@
         <v>1399</v>
       </c>
     </row>
-    <row r="890" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A890" s="7" t="s">
         <v>757</v>
       </c>
@@ -22324,7 +22513,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="891" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A891" s="7" t="s">
         <v>341</v>
       </c>
@@ -22342,7 +22531,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="892" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A892" s="7" t="s">
         <v>758</v>
       </c>
@@ -22363,7 +22552,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="893" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A893" s="7" t="s">
         <v>759</v>
       </c>
@@ -22384,7 +22573,7 @@
         <v>1402</v>
       </c>
     </row>
-    <row r="894" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A894" s="7" t="s">
         <v>430</v>
       </c>
@@ -22405,7 +22594,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="895" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A895" s="7" t="s">
         <v>760</v>
       </c>
@@ -22423,7 +22612,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="896" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A896" s="7" t="s">
         <v>343</v>
       </c>
@@ -22444,7 +22633,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="897" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A897" s="7" t="s">
         <v>761</v>
       </c>
@@ -22462,7 +22651,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="898" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A898" s="7" t="s">
         <v>762</v>
       </c>
@@ -22483,7 +22672,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="899" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A899" s="7" t="s">
         <v>763</v>
       </c>
@@ -22491,7 +22680,7 @@
         <v>1430</v>
       </c>
       <c r="C899" s="1" t="b">
-        <f t="shared" ref="C899:C935" si="14">ISNUMBER(SEARCH("trimethylsilyl",A899))</f>
+        <f t="shared" ref="C899:C935" si="14">ISNUMBER(SEARCH("silyl",A899))</f>
         <v>0</v>
       </c>
       <c r="D899">
@@ -22501,7 +22690,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="900" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A900" s="7" t="s">
         <v>764</v>
       </c>
@@ -22531,7 +22720,7 @@
       </c>
       <c r="C901" s="1" t="b">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="902" spans="1:6" x14ac:dyDescent="0.25">
@@ -22543,10 +22732,10 @@
       </c>
       <c r="C902" s="1" t="b">
         <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="903" spans="1:6" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="903" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A903" s="7" t="s">
         <v>767</v>
       </c>
@@ -22567,7 +22756,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="904" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A904" s="7" t="s">
         <v>768</v>
       </c>
@@ -22585,7 +22774,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="905" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A905" s="7" t="s">
         <v>769</v>
       </c>
@@ -22603,7 +22792,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="906" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A906" s="7" t="s">
         <v>770</v>
       </c>
@@ -22615,7 +22804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="907" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A907" s="7" t="s">
         <v>771</v>
       </c>
@@ -22627,7 +22816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="908" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A908" s="7" t="s">
         <v>772</v>
       </c>
@@ -22645,7 +22834,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="909" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A909" s="7" t="s">
         <v>355</v>
       </c>
@@ -22663,7 +22852,7 @@
         <v>1090</v>
       </c>
     </row>
-    <row r="910" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A910" s="7" t="s">
         <v>773</v>
       </c>
@@ -22684,7 +22873,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="911" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A911" s="7" t="s">
         <v>774</v>
       </c>
@@ -22702,7 +22891,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="912" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A912" s="7" t="s">
         <v>775</v>
       </c>
@@ -22720,7 +22909,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="913" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A913" s="7" t="s">
         <v>358</v>
       </c>
@@ -22741,7 +22930,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="914" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A914" s="7" t="s">
         <v>360</v>
       </c>
@@ -22762,7 +22951,7 @@
         <v>1094</v>
       </c>
     </row>
-    <row r="915" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A915" s="7" t="s">
         <v>776</v>
       </c>
@@ -22783,7 +22972,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="916" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A916" s="7" t="s">
         <v>777</v>
       </c>
@@ -22804,7 +22993,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="917" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A917" s="7" t="s">
         <v>402</v>
       </c>
@@ -22825,7 +23014,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="918" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A918" s="7" t="s">
         <v>778</v>
       </c>
@@ -22846,7 +23035,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="919" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A919" s="7" t="s">
         <v>779</v>
       </c>
@@ -22876,7 +23065,7 @@
       </c>
       <c r="C920" s="1" t="b">
         <f t="shared" si="14"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D920">
         <v>6430553</v>
@@ -22885,7 +23074,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="921" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A921" s="7" t="s">
         <v>781</v>
       </c>
@@ -22903,7 +23092,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="922" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A922" s="7" t="s">
         <v>782</v>
       </c>
@@ -22921,7 +23110,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="923" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A923" s="7" t="s">
         <v>783</v>
       </c>
@@ -22939,7 +23128,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="924" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A924" s="7" t="s">
         <v>784</v>
       </c>
@@ -22960,7 +23149,7 @@
         <v>1423</v>
       </c>
     </row>
-    <row r="925" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A925" s="7" t="s">
         <v>785</v>
       </c>
@@ -22981,7 +23170,7 @@
         <v>1424</v>
       </c>
     </row>
-    <row r="926" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A926" s="7" t="s">
         <v>786</v>
       </c>
@@ -23002,7 +23191,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="927" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A927" s="7" t="s">
         <v>787</v>
       </c>
@@ -23020,7 +23209,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="928" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A928" s="7" t="s">
         <v>788</v>
       </c>
@@ -23041,7 +23230,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="929" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A929" s="7" t="s">
         <v>789</v>
       </c>
@@ -23059,7 +23248,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="930" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A930" s="7" t="s">
         <v>371</v>
       </c>
@@ -23080,7 +23269,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="931" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A931" s="7" t="s">
         <v>395</v>
       </c>
@@ -23101,7 +23290,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="932" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A932" s="7" t="s">
         <v>372</v>
       </c>
@@ -23119,7 +23308,7 @@
         <v>1109</v>
       </c>
     </row>
-    <row r="933" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A933" s="7" t="s">
         <v>790</v>
       </c>
@@ -23137,7 +23326,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="934" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A934" s="7" t="s">
         <v>373</v>
       </c>
@@ -23155,7 +23344,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="935" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A935" s="7" t="s">
         <v>791</v>
       </c>
@@ -23177,7 +23366,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F935" xr:uid="{922CBA57-B4CC-9E42-A0F6-E5FE0A9FA5EC}"/>
+  <autoFilter ref="A1:F935" xr:uid="{922CBA57-B4CC-9E42-A0F6-E5FE0A9FA5EC}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="TRUE"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="D1:F1 C1:C1048576">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>FALSE</formula>
@@ -23188,4 +23383,674 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F74EA60A-F317-264B-8424-78A87D50A412}">
+  <dimension ref="A1:C67"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="87.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="38" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1822</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C2">
+        <v>91696873</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>1763</v>
+      </c>
+      <c r="C3">
+        <v>91706643</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>1767</v>
+      </c>
+      <c r="C4">
+        <v>601546</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>1764</v>
+      </c>
+      <c r="C5">
+        <v>142239</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>1765</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C7">
+        <v>91740490</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>1816</v>
+      </c>
+      <c r="C8">
+        <v>588565</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>1768</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>1769</v>
+      </c>
+      <c r="C11">
+        <v>91736840</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A13" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C13">
+        <v>91696644</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A14" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>1771</v>
+      </c>
+      <c r="C14">
+        <v>601551</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A15" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A16" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>1773</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A17" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C17">
+        <v>84564</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A19" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>1776</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A20" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>1817</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A21" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>1777</v>
+      </c>
+      <c r="C21">
+        <v>91741325</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A22" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C22">
+        <v>533404</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A24" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C25">
+        <v>18935209</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>1781</v>
+      </c>
+      <c r="C26">
+        <v>91729087</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A27" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>1782</v>
+      </c>
+      <c r="C27">
+        <v>530172</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A28" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>1783</v>
+      </c>
+      <c r="C28">
+        <v>3015764</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A29" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A30" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>1784</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A32" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>1788</v>
+      </c>
+      <c r="C32">
+        <v>81705</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A34" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>1787</v>
+      </c>
+      <c r="C34">
+        <v>553578</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C35">
+        <v>91733438</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>1792</v>
+      </c>
+      <c r="C36">
+        <v>637748</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C37">
+        <v>533405</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>1790</v>
+      </c>
+      <c r="C38">
+        <v>91733438</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A39" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>1791</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>540</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>1793</v>
+      </c>
+      <c r="C40">
+        <v>91742919</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>546</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C41">
+        <v>14345506</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C42">
+        <v>91716313</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
+        <v>553</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>1796</v>
+      </c>
+      <c r="C43">
+        <v>553703</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>1797</v>
+      </c>
+      <c r="C44">
+        <v>5378122</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>1798</v>
+      </c>
+      <c r="C45">
+        <v>575921</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>1799</v>
+      </c>
+      <c r="C46">
+        <v>91741551</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A47" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C49">
+        <v>554546</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A50" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>1802</v>
+      </c>
+      <c r="C50">
+        <v>91697039</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A51" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>1803</v>
+      </c>
+      <c r="C51">
+        <v>10357235</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A52" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C52">
+        <v>575923</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A53" s="8" t="s">
+        <v>638</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C53">
+        <v>91697308</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A54" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>1806</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A55" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>1807</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
+        <v>653</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>1808</v>
+      </c>
+      <c r="C56">
+        <v>91740788</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A57" s="8" t="s">
+        <v>687</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A58" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A59" s="8" t="s">
+        <v>706</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C59">
+        <v>19104051</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A60" s="8" t="s">
+        <v>713</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A61" s="8" t="s">
+        <v>718</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A62" s="8" t="s">
+        <v>743</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>1811</v>
+      </c>
+      <c r="C62">
+        <v>91693841</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A63" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A64" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C64">
+        <v>91697075</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A65" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>1814</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A66" s="8" t="s">
+        <v>766</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>1815</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="18" x14ac:dyDescent="0.25">
+      <c r="A67" s="8" t="s">
+        <v>780</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>1821</v>
+      </c>
+      <c r="C67">
+        <v>6430553</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>